--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -538,13 +538,13 @@
     <t>20122571</t>
   </si>
   <si>
-    <t>PIATTOS SAPI PG 120G</t>
+    <t>PIATTOS SAPI PG 115G</t>
   </si>
   <si>
     <t>20134572</t>
   </si>
   <si>
-    <t>PIATTOS SMB GPREK120</t>
+    <t>PIATTOS SMB GPRK 115</t>
   </si>
   <si>
     <t>20119437</t>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="523">
   <si>
     <t/>
   </si>
@@ -253,123 +253,117 @@
     <t>MR/P GHST/P SWEED40</t>
   </si>
   <si>
-    <t>20120199</t>
-  </si>
-  <si>
-    <t>MR/P GHST/P CHEESE40</t>
+    <t>20141098</t>
+  </si>
+  <si>
+    <t>MR PTT BULDAK CHES40</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20141098</t>
-  </si>
-  <si>
-    <t>MR PTT BULDAK CHES40</t>
+    <t>20139841</t>
+  </si>
+  <si>
+    <t>MR POTATO CRBNARA 40</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>20139841</t>
-  </si>
-  <si>
-    <t>MR POTATO CRBNARA 40</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139544</t>
+  </si>
+  <si>
+    <t>LAYS STAX SOUR&amp;O 70G</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139544</t>
-  </si>
-  <si>
-    <t>LAYS STAX SOUR&amp;O 70G</t>
+    <t>20139536</t>
+  </si>
+  <si>
+    <t>LAYS STAX ORGNL 70G</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>20139536</t>
-  </si>
-  <si>
-    <t>LAYS STAX ORGNL 70G</t>
+    <t>20023846</t>
+  </si>
+  <si>
+    <t>PRNGLES ORIGNAL 102G</t>
+  </si>
+  <si>
+    <t>20023845</t>
+  </si>
+  <si>
+    <t>PRINGLES CHEESY 102G</t>
+  </si>
+  <si>
+    <t>20044093</t>
+  </si>
+  <si>
+    <t>PRNGLES S.CRM&amp;O 102G</t>
+  </si>
+  <si>
+    <t>20141457</t>
+  </si>
+  <si>
+    <t>PRLGS BR SWD 102</t>
+  </si>
+  <si>
+    <t>RT,(E-27H)</t>
+  </si>
+  <si>
+    <t>20136007</t>
+  </si>
+  <si>
+    <t>MR.POTATO BBQ 85G</t>
+  </si>
+  <si>
+    <t>20135539</t>
+  </si>
+  <si>
+    <t>MR.POTATO ORGINAL85G</t>
+  </si>
+  <si>
+    <t>20135538</t>
+  </si>
+  <si>
+    <t>MR.POTATO SOUR&amp;O 85G</t>
+  </si>
+  <si>
+    <t>20137054</t>
+  </si>
+  <si>
+    <t>CHTATO LITE ASLI 110</t>
+  </si>
+  <si>
+    <t>20137572</t>
+  </si>
+  <si>
+    <t>CHTATO LITE KEJU 110</t>
+  </si>
+  <si>
+    <t>10000739</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PANG.35</t>
+  </si>
+  <si>
+    <t>20092063</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PGG 115</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>20023846</t>
-  </si>
-  <si>
-    <t>PRNGLES ORIGNAL 102G</t>
-  </si>
-  <si>
-    <t>20023845</t>
-  </si>
-  <si>
-    <t>PRINGLES CHEESY 102G</t>
-  </si>
-  <si>
-    <t>20044093</t>
-  </si>
-  <si>
-    <t>PRNGLES S.CRM&amp;O 102G</t>
-  </si>
-  <si>
-    <t>20141457</t>
-  </si>
-  <si>
-    <t>PRLGS BR SWD 102</t>
-  </si>
-  <si>
-    <t>RT,(E-27H)</t>
-  </si>
-  <si>
-    <t>20136007</t>
-  </si>
-  <si>
-    <t>MR.POTATO BBQ 85G</t>
-  </si>
-  <si>
-    <t>20135539</t>
-  </si>
-  <si>
-    <t>MR.POTATO ORGINAL85G</t>
-  </si>
-  <si>
-    <t>20135538</t>
-  </si>
-  <si>
-    <t>MR.POTATO SOUR&amp;O 85G</t>
-  </si>
-  <si>
-    <t>20137054</t>
-  </si>
-  <si>
-    <t>CHTATO LITE ASLI 110</t>
-  </si>
-  <si>
-    <t>20137572</t>
-  </si>
-  <si>
-    <t>CHTATO LITE KEJU 110</t>
-  </si>
-  <si>
-    <t>10000739</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PANG.35</t>
-  </si>
-  <si>
-    <t>20092063</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 115</t>
-  </si>
-  <si>
     <t>20002987</t>
   </si>
   <si>
@@ -1153,10 +1147,10 @@
     <t>JETZ CROISANT CHOC50</t>
   </si>
   <si>
-    <t>20137069</t>
-  </si>
-  <si>
-    <t>KUSUKA UBI BBQ 42G</t>
+    <t>20139969</t>
+  </si>
+  <si>
+    <t>GERY SNAK BANTAL 75G</t>
   </si>
   <si>
     <t>20004229</t>
@@ -1165,15 +1159,27 @@
     <t>SMAX RING CHEESE 40G</t>
   </si>
   <si>
+    <t>10000752</t>
+  </si>
+  <si>
+    <t>TARO SNACK BARBQ 32G</t>
+  </si>
+  <si>
+    <t>20097777</t>
+  </si>
+  <si>
+    <t>KRISBEE PLW CHO 100G</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>20081238</t>
   </si>
   <si>
     <t>TARO NET TRYK BBQ 62</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>20055205</t>
   </si>
   <si>
@@ -1192,12 +1198,6 @@
     <t>TARO SNACK SEAWED 32</t>
   </si>
   <si>
-    <t>10000752</t>
-  </si>
-  <si>
-    <t>TARO SNACK BARBQ 32G</t>
-  </si>
-  <si>
     <t>20069696</t>
   </si>
   <si>
@@ -1247,12 +1247,6 @@
   </si>
   <si>
     <t>OISHI PILLOW CHO 100</t>
-  </si>
-  <si>
-    <t>20097777</t>
-  </si>
-  <si>
-    <t>KRISBEE PLW CHO 100G</t>
   </si>
   <si>
     <t>20141746</t>
@@ -1978,7 +1972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F239"/>
+  <dimension ref="A1:F238"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2725,15 +2719,15 @@
         <v>85</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2742,10 +2736,10 @@
         <v>22</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2779,10 +2773,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>37</v>
@@ -2790,10 +2784,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2802,7 +2796,7 @@
         <v>82</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>37</v>
@@ -2810,10 +2804,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2822,7 +2816,7 @@
         <v>82</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>37</v>
@@ -2830,10 +2824,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2842,10 +2836,10 @@
         <v>82</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2862,18 +2856,18 @@
         <v>82</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>104</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2882,7 +2876,7 @@
         <v>82</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>37</v>
@@ -2890,10 +2884,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2902,7 +2896,7 @@
         <v>82</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>37</v>
@@ -2910,10 +2904,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2922,18 +2916,18 @@
         <v>82</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2942,7 +2936,7 @@
         <v>82</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2950,10 +2944,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2962,7 +2956,7 @@
         <v>82</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2970,10 +2964,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2982,7 +2976,7 @@
         <v>82</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2999,13 +2993,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3022,7 +3016,7 @@
         <v>85</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>19</v>
@@ -3042,7 +3036,7 @@
         <v>85</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>19</v>
@@ -3062,7 +3056,7 @@
         <v>85</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>19</v>
@@ -3082,10 +3076,10 @@
         <v>85</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3102,7 +3096,7 @@
         <v>85</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -3122,7 +3116,7 @@
         <v>85</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -3139,13 +3133,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3159,10 +3153,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>37</v>
@@ -3179,33 +3173,33 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3219,13 +3213,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>139</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3239,10 +3233,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3259,10 +3253,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3279,13 +3273,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3302,18 +3296,18 @@
         <v>92</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>37</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -3322,10 +3316,10 @@
         <v>92</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3342,10 +3336,10 @@
         <v>92</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3362,7 +3356,7 @@
         <v>92</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>19</v>
@@ -3379,13 +3373,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3399,10 +3393,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3419,10 +3413,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3439,10 +3433,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3459,13 +3453,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3479,33 +3473,33 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3519,13 +3513,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3539,10 +3533,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>19</v>
@@ -3559,13 +3553,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3579,33 +3573,33 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="E81" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3619,13 +3613,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3639,10 +3633,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3659,13 +3653,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3679,10 +3673,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>12</v>
@@ -3690,19 +3684,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>12</v>
@@ -3719,13 +3713,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3739,13 +3733,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3759,10 +3753,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>37</v>
@@ -3779,10 +3773,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>37</v>
@@ -3799,10 +3793,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>37</v>
@@ -3810,19 +3804,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>37</v>
@@ -3839,13 +3833,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3859,13 +3853,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3879,10 +3873,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>37</v>
@@ -3899,10 +3893,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>37</v>
@@ -3910,22 +3904,22 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3939,13 +3933,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3959,13 +3953,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3979,13 +3973,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3999,10 +3993,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>37</v>
@@ -4019,10 +4013,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>37</v>
@@ -4030,19 +4024,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>37</v>
@@ -4059,10 +4053,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>37</v>
@@ -4079,13 +4073,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4099,13 +4093,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4119,33 +4113,33 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4159,13 +4153,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4179,10 +4173,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>37</v>
@@ -4199,13 +4193,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4219,10 +4213,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -4239,30 +4233,30 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4279,10 +4273,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4299,13 +4293,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4319,10 +4313,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -4339,30 +4333,30 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4379,10 +4373,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4399,10 +4393,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -4419,13 +4413,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4439,50 +4433,50 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>37</v>
+        <v>274</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>276</v>
+        <v>37</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>37</v>
@@ -4499,10 +4493,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>37</v>
@@ -4519,13 +4513,13 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4539,13 +4533,13 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>274</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4559,30 +4553,30 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>276</v>
+        <v>37</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>37</v>
@@ -4599,10 +4593,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>37</v>
@@ -4619,13 +4613,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4639,13 +4633,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4659,10 +4653,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>37</v>
@@ -4679,10 +4673,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>37</v>
@@ -4690,19 +4684,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>37</v>
@@ -4719,10 +4713,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>37</v>
@@ -4739,10 +4733,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>37</v>
@@ -4759,10 +4753,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>37</v>
@@ -4770,19 +4764,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>37</v>
@@ -4799,10 +4793,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>37</v>
@@ -4819,10 +4813,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>37</v>
@@ -4839,10 +4833,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>37</v>
@@ -4859,10 +4853,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>37</v>
@@ -4870,19 +4864,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>37</v>
@@ -4899,13 +4893,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4919,10 +4913,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>19</v>
@@ -4939,13 +4933,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4959,30 +4953,30 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>37</v>
@@ -4999,10 +4993,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>37</v>
@@ -5019,10 +5013,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>37</v>
@@ -5039,10 +5033,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>37</v>
@@ -5059,13 +5053,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5079,13 +5073,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5099,13 +5093,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5119,10 +5113,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>37</v>
@@ -5130,22 +5124,22 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5159,10 +5153,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>19</v>
@@ -5179,10 +5173,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>19</v>
@@ -5199,10 +5193,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>19</v>
@@ -5219,13 +5213,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5239,10 +5233,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>37</v>
@@ -5250,19 +5244,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>37</v>
@@ -5279,13 +5273,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5299,10 +5293,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5319,10 +5313,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5339,33 +5333,33 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5379,13 +5373,13 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5399,13 +5393,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5419,13 +5413,13 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5439,13 +5433,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5465,7 +5459,7 @@
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5722,10 +5716,10 @@
         <v>397</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5739,30 +5733,30 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="E189" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>12</v>
@@ -5779,13 +5773,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5799,10 +5793,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5819,13 +5813,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5839,10 +5833,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>37</v>
@@ -5859,10 +5853,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>37</v>
@@ -5879,13 +5873,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5899,30 +5893,30 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>435</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>37</v>
@@ -5939,10 +5933,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>37</v>
@@ -5959,13 +5953,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -5979,13 +5973,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5999,10 +5993,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>37</v>
@@ -6019,10 +6013,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>37</v>
@@ -6030,19 +6024,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="E203" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>37</v>
@@ -6059,10 +6053,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>37</v>
@@ -6079,10 +6073,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>37</v>
@@ -6099,10 +6093,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>37</v>
@@ -6119,10 +6113,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>37</v>
@@ -6139,10 +6133,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>37</v>
@@ -6150,19 +6144,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D209" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="E209" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>37</v>
@@ -6179,10 +6173,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>37</v>
@@ -6199,10 +6193,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>37</v>
@@ -6219,10 +6213,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>37</v>
@@ -6239,10 +6233,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>37</v>
@@ -6259,10 +6253,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>37</v>
@@ -6279,10 +6273,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>37</v>
@@ -6290,19 +6284,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="E216" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>37</v>
@@ -6319,10 +6313,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>37</v>
@@ -6339,10 +6333,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>37</v>
@@ -6359,10 +6353,10 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>37</v>
@@ -6379,10 +6373,10 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>37</v>
@@ -6399,10 +6393,10 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>37</v>
@@ -6419,10 +6413,10 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>37</v>
@@ -6430,19 +6424,19 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D223" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>491</v>
-      </c>
       <c r="E223" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>37</v>
@@ -6459,10 +6453,10 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>37</v>
@@ -6479,13 +6473,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6499,13 +6493,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6519,13 +6513,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6539,13 +6533,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>89</v>
+        <v>19</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6559,13 +6553,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6579,33 +6573,33 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D231" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>508</v>
-      </c>
       <c r="E231" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -6619,13 +6613,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -6639,13 +6633,13 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -6659,13 +6653,13 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -6679,10 +6673,10 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>37</v>
@@ -6699,10 +6693,10 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>37</v>
@@ -6719,10 +6713,10 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>37</v>
@@ -6739,32 +6733,12 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A239" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="C239" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D239" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="E239" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F239" s="1" t="s">
         <v>37</v>
       </c>
     </row>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="515">
   <si>
     <t/>
   </si>
@@ -181,6 +181,12 @@
     <t>CHITATO TTEOK-BK 65G</t>
   </si>
   <si>
+    <t>20141944</t>
+  </si>
+  <si>
+    <t>CHITATO RNDG SAPI 62</t>
+  </si>
+  <si>
     <t>10001094</t>
   </si>
   <si>
@@ -1018,24 +1024,12 @@
     <t>TAO KAE CRSPY ORG 15</t>
   </si>
   <si>
-    <t>20137779</t>
-  </si>
-  <si>
-    <t>TAO KAE/N WGYU 6G</t>
-  </si>
-  <si>
     <t>20024856</t>
   </si>
   <si>
     <t>TAO KAE CLASSIC 3.2G</t>
   </si>
   <si>
-    <t>20137577</t>
-  </si>
-  <si>
-    <t>TKN SPICY MAYO 3.2G</t>
-  </si>
-  <si>
     <t>20072581</t>
   </si>
   <si>
@@ -1126,27 +1120,15 @@
     <t>GURIBEE KEJU 65G</t>
   </si>
   <si>
-    <t>20138466</t>
-  </si>
-  <si>
-    <t>NABATI AHH STRW 30G</t>
+    <t>20141505</t>
+  </si>
+  <si>
+    <t>JETZ CROISANT CHOC50</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>20135812</t>
-  </si>
-  <si>
-    <t>NABATI RCHSE AHH 30G</t>
-  </si>
-  <si>
-    <t>20141505</t>
-  </si>
-  <si>
-    <t>JETZ CROISANT CHOC50</t>
-  </si>
-  <si>
     <t>20139969</t>
   </si>
   <si>
@@ -1262,12 +1244,6 @@
   </si>
   <si>
     <t>32</t>
-  </si>
-  <si>
-    <t>20129035</t>
-  </si>
-  <si>
-    <t>S/N SS AYM.BWG 2X40G</t>
   </si>
   <si>
     <t>10024188</t>
@@ -1972,7 +1948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F238"/>
+  <dimension ref="A1:F234"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2453,10 +2429,10 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -2476,7 +2452,7 @@
         <v>18</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -2496,7 +2472,7 @@
         <v>18</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2516,7 +2492,7 @@
         <v>18</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -2536,7 +2512,7 @@
         <v>18</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2556,7 +2532,7 @@
         <v>18</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2573,13 +2549,13 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2596,7 +2572,7 @@
         <v>22</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>37</v>
@@ -2616,7 +2592,7 @@
         <v>22</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>37</v>
@@ -2636,7 +2612,7 @@
         <v>22</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>37</v>
@@ -2656,7 +2632,7 @@
         <v>22</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>37</v>
@@ -2676,7 +2652,7 @@
         <v>22</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>37</v>
@@ -2696,7 +2672,7 @@
         <v>22</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>37</v>
@@ -2704,10 +2680,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2716,18 +2692,18 @@
         <v>22</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2736,18 +2712,18 @@
         <v>22</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2756,7 +2732,7 @@
         <v>22</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>37</v>
@@ -2764,19 +2740,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>37</v>
@@ -2793,10 +2769,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>37</v>
@@ -2813,10 +2789,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>37</v>
@@ -2833,33 +2809,33 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2873,10 +2849,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>37</v>
@@ -2893,10 +2869,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>37</v>
@@ -2913,13 +2889,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2933,10 +2909,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2953,10 +2929,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2973,10 +2949,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2984,22 +2960,22 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3013,10 +2989,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>19</v>
@@ -3033,10 +3009,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>19</v>
@@ -3053,10 +3029,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>19</v>
@@ -3073,13 +3049,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3093,10 +3069,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -3113,10 +3089,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -3133,13 +3109,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3153,10 +3129,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>37</v>
@@ -3173,33 +3149,33 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3213,13 +3189,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3233,10 +3209,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3253,10 +3229,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3273,13 +3249,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3293,33 +3269,33 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>150</v>
+        <v>37</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3333,13 +3309,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>19</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3353,10 +3329,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>19</v>
@@ -3373,13 +3349,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3393,10 +3369,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3413,10 +3389,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3433,10 +3409,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3453,13 +3429,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3473,33 +3449,33 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3513,13 +3489,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3533,10 +3509,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>19</v>
@@ -3553,13 +3529,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3573,33 +3549,33 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3613,13 +3589,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3633,10 +3609,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3653,13 +3629,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3673,10 +3649,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>12</v>
@@ -3684,19 +3660,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>12</v>
@@ -3713,13 +3689,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3733,13 +3709,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3753,10 +3729,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>37</v>
@@ -3773,10 +3749,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>37</v>
@@ -3793,10 +3769,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>37</v>
@@ -3804,19 +3780,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>37</v>
@@ -3833,13 +3809,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3853,13 +3829,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3873,10 +3849,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>37</v>
@@ -3893,10 +3869,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>37</v>
@@ -3904,22 +3880,22 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="C97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3933,13 +3909,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3953,13 +3929,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3973,13 +3949,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3993,10 +3969,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>37</v>
@@ -4013,10 +3989,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>37</v>
@@ -4024,19 +4000,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>37</v>
@@ -4053,10 +4029,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>37</v>
@@ -4073,13 +4049,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4093,13 +4069,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4113,33 +4089,33 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4153,13 +4129,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4173,10 +4149,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>37</v>
@@ -4193,13 +4169,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4213,10 +4189,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -4233,30 +4209,30 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4273,10 +4249,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4293,13 +4269,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4313,10 +4289,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -4333,30 +4309,30 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4373,10 +4349,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4393,10 +4369,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -4413,13 +4389,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4433,50 +4409,50 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>274</v>
+        <v>37</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="E125" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>37</v>
@@ -4493,10 +4469,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>37</v>
@@ -4513,13 +4489,13 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4533,13 +4509,13 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>274</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4553,30 +4529,30 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>37</v>
+        <v>276</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>37</v>
@@ -4593,10 +4569,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>37</v>
@@ -4613,13 +4589,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4633,13 +4609,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4653,10 +4629,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>37</v>
@@ -4673,10 +4649,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>37</v>
@@ -4684,19 +4660,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>37</v>
@@ -4713,10 +4689,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>37</v>
@@ -4733,10 +4709,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>37</v>
@@ -4753,10 +4729,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>37</v>
@@ -4764,19 +4740,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>37</v>
@@ -4793,10 +4769,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>37</v>
@@ -4813,10 +4789,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>37</v>
@@ -4833,10 +4809,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>37</v>
@@ -4853,10 +4829,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>37</v>
@@ -4864,19 +4840,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="E145" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>37</v>
@@ -4893,13 +4869,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4913,10 +4889,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>19</v>
@@ -4933,13 +4909,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4953,30 +4929,30 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="E150" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>37</v>
@@ -4993,10 +4969,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>37</v>
@@ -5013,7 +4989,7 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>15</v>
@@ -5033,13 +5009,13 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5053,13 +5029,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5073,13 +5049,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5093,10 +5069,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>37</v>
@@ -5104,22 +5080,22 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5133,10 +5109,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>19</v>
@@ -5153,10 +5129,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>19</v>
@@ -5173,10 +5149,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>19</v>
@@ -5193,13 +5169,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5213,10 +5189,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>37</v>
@@ -5224,19 +5200,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>37</v>
@@ -5253,13 +5229,13 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5273,10 +5249,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5293,10 +5269,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5313,10 +5289,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5324,22 +5300,22 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="E168" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5353,10 +5329,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>37</v>
@@ -5373,13 +5349,13 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5393,50 +5369,50 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="E172" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>19</v>
@@ -5444,22 +5420,22 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5473,10 +5449,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>19</v>
@@ -5493,70 +5469,70 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="E177" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>37</v>
@@ -5573,10 +5549,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>37</v>
@@ -5593,10 +5569,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>37</v>
@@ -5613,10 +5589,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>37</v>
@@ -5633,10 +5609,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>37</v>
@@ -5653,10 +5629,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>37</v>
@@ -5673,73 +5649,73 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="E186" s="1" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -5753,13 +5729,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5773,13 +5749,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5793,10 +5769,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5813,10 +5789,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>37</v>
@@ -5824,19 +5800,19 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>416</v>
-      </c>
       <c r="E193" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>37</v>
@@ -5844,19 +5820,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>37</v>
@@ -5864,39 +5840,39 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>5</v>
+        <v>88</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>37</v>
@@ -5913,10 +5889,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>37</v>
@@ -5933,10 +5909,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>37</v>
@@ -5944,39 +5920,39 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="E199" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>37</v>
@@ -5984,19 +5960,19 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>37</v>
@@ -6004,19 +5980,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>37</v>
@@ -6033,10 +6009,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>37</v>
@@ -6053,10 +6029,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>37</v>
@@ -6064,19 +6040,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="E205" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>37</v>
@@ -6084,19 +6060,19 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>37</v>
@@ -6104,19 +6080,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>37</v>
@@ -6124,19 +6100,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>37</v>
@@ -6153,10 +6129,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>37</v>
@@ -6173,10 +6149,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>37</v>
@@ -6193,10 +6169,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>37</v>
@@ -6204,19 +6180,19 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="E212" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>37</v>
@@ -6224,19 +6200,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>37</v>
@@ -6244,19 +6220,19 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>37</v>
@@ -6264,19 +6240,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>37</v>
@@ -6293,10 +6269,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>37</v>
@@ -6313,10 +6289,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>37</v>
@@ -6333,10 +6309,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>37</v>
@@ -6344,19 +6320,19 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="E219" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>37</v>
@@ -6364,19 +6340,19 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>37</v>
@@ -6384,42 +6360,42 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6433,13 +6409,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6453,13 +6429,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6473,13 +6449,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6493,93 +6469,93 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D227" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D227" s="1" t="s">
-        <v>489</v>
-      </c>
       <c r="E227" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6593,13 +6569,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -6613,13 +6589,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -6633,13 +6609,13 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -6653,92 +6629,12 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E235" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F235" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A236" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D236" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E236" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F236" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A237" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E237" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F237" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A238" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D238" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E238" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F238" s="1" t="s">
         <v>37</v>
       </c>
     </row>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="516">
   <si>
     <t/>
   </si>
@@ -388,12 +388,6 @@
     <t>KUSUKA RMPT LAUT 60</t>
   </si>
   <si>
-    <t>20002989</t>
-  </si>
-  <si>
-    <t>KUSUKA KRP KJ.BKR 60</t>
-  </si>
-  <si>
     <t>20056958</t>
   </si>
   <si>
@@ -625,21 +619,15 @@
     <t>KRAKER UDANG PDS 60</t>
   </si>
   <si>
-    <t>20137565</t>
-  </si>
-  <si>
-    <t>CRUNCHY TWSTR BBQ 60</t>
+    <t>20124707</t>
+  </si>
+  <si>
+    <t>GRD O'CORN JG/BKR 70</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>20124707</t>
-  </si>
-  <si>
-    <t>GRD O'CORN JG/BKR 70</t>
-  </si>
-  <si>
     <t>20139291</t>
   </si>
   <si>
@@ -712,6 +700,12 @@
     <t>DORITOS JGG BKR 120G</t>
   </si>
   <si>
+    <t>20142266</t>
+  </si>
+  <si>
+    <t>DORITOS NCHO CHS 120</t>
+  </si>
+  <si>
     <t>20131013</t>
   </si>
   <si>
@@ -844,13 +838,22 @@
     <t>RT,(E-15H)</t>
   </si>
   <si>
+    <t>20142265</t>
+  </si>
+  <si>
+    <t>WONHAE TPKI CHS BU80</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
     <t>20132657</t>
   </si>
   <si>
     <t>WONHAE TPKI CRM.RS80</t>
-  </si>
-  <si>
-    <t>21</t>
   </si>
   <si>
     <t>20139930</t>
@@ -3052,10 +3055,10 @@
         <v>87</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3072,7 +3075,7 @@
         <v>87</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -3092,7 +3095,7 @@
         <v>87</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -3109,13 +3112,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3132,7 +3135,7 @@
         <v>91</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>37</v>
@@ -3152,18 +3155,18 @@
         <v>91</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -3172,10 +3175,10 @@
         <v>91</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3192,10 +3195,10 @@
         <v>91</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>139</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3212,7 +3215,7 @@
         <v>91</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3232,7 +3235,7 @@
         <v>91</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3249,13 +3252,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3272,18 +3275,18 @@
         <v>94</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>37</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -3292,10 +3295,10 @@
         <v>94</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3312,10 +3315,10 @@
         <v>94</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3332,7 +3335,7 @@
         <v>94</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>19</v>
@@ -3349,13 +3352,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3372,7 +3375,7 @@
         <v>118</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3392,7 +3395,7 @@
         <v>118</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3412,7 +3415,7 @@
         <v>118</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3432,10 +3435,10 @@
         <v>118</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3449,33 +3452,33 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3489,13 +3492,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3509,10 +3512,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>19</v>
@@ -3529,13 +3532,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3549,33 +3552,33 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="E81" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3589,13 +3592,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3609,10 +3612,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3629,13 +3632,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3649,10 +3652,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>12</v>
@@ -3660,19 +3663,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>12</v>
@@ -3689,13 +3692,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3709,13 +3712,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3729,10 +3732,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>37</v>
@@ -3749,10 +3752,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>37</v>
@@ -3769,10 +3772,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>37</v>
@@ -3780,22 +3783,22 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3809,10 +3812,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>37</v>
@@ -3829,13 +3832,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3849,10 +3852,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>37</v>
@@ -3860,39 +3863,39 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>37</v>
@@ -3909,13 +3912,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3929,10 +3932,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>37</v>
@@ -3949,13 +3952,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3969,10 +3972,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>37</v>
@@ -3980,19 +3983,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>37</v>
@@ -4000,19 +4003,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>37</v>
@@ -4029,10 +4032,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>37</v>
@@ -4049,13 +4052,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4069,13 +4072,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4089,33 +4092,33 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4129,13 +4132,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4149,10 +4152,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>37</v>
@@ -4169,13 +4172,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4189,10 +4192,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -4209,30 +4212,30 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4249,10 +4252,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4269,13 +4272,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4289,10 +4292,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -4309,30 +4312,30 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4349,10 +4352,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4369,10 +4372,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -4389,13 +4392,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4409,50 +4412,50 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>37</v>
+        <v>274</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>37</v>
@@ -4460,19 +4463,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>37</v>
@@ -4480,19 +4483,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>37</v>
@@ -4500,19 +4503,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4520,36 +4523,36 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>4</v>
@@ -4560,16 +4563,16 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>8</v>
@@ -4580,16 +4583,16 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>11</v>
@@ -4600,16 +4603,16 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>15</v>
@@ -4620,16 +4623,16 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>18</v>
@@ -4640,16 +4643,16 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>22</v>
@@ -4660,16 +4663,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>4</v>
@@ -4680,16 +4683,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>8</v>
@@ -4700,16 +4703,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>11</v>
@@ -4720,16 +4723,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>15</v>
@@ -4740,16 +4743,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>4</v>
@@ -4760,16 +4763,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>8</v>
@@ -4780,16 +4783,16 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>11</v>
@@ -4800,16 +4803,16 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>15</v>
@@ -4820,16 +4823,16 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>18</v>
@@ -4840,16 +4843,16 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>4</v>
@@ -4860,16 +4863,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>8</v>
@@ -4880,16 +4883,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>11</v>
@@ -4900,16 +4903,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>15</v>
@@ -4920,16 +4923,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>18</v>
@@ -4940,16 +4943,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>4</v>
@@ -4960,16 +4963,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>8</v>
@@ -4980,16 +4983,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>15</v>
@@ -5000,16 +5003,16 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>22</v>
@@ -5020,16 +5023,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>84</v>
@@ -5040,16 +5043,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>87</v>
@@ -5060,16 +5063,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>4</v>
@@ -5080,16 +5083,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>8</v>
@@ -5100,16 +5103,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>11</v>
@@ -5120,16 +5123,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>15</v>
@@ -5140,16 +5143,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>18</v>
@@ -5160,16 +5163,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>22</v>
@@ -5180,16 +5183,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>4</v>
@@ -5200,16 +5203,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>360</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>8</v>
@@ -5220,16 +5223,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>11</v>
@@ -5240,16 +5243,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>15</v>
@@ -5260,16 +5263,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>18</v>
@@ -5280,16 +5283,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>15</v>
@@ -5300,16 +5303,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>18</v>
@@ -5320,16 +5323,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>22</v>
@@ -5340,16 +5343,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>84</v>
@@ -5360,16 +5363,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>4</v>
@@ -5380,16 +5383,16 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>8</v>
@@ -5400,16 +5403,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>11</v>
@@ -5420,16 +5423,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>15</v>
@@ -5440,16 +5443,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>18</v>
@@ -5460,16 +5463,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>4</v>
@@ -5480,16 +5483,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>8</v>
@@ -5500,16 +5503,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>11</v>
@@ -5520,16 +5523,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>15</v>
@@ -5540,16 +5543,16 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>18</v>
@@ -5560,16 +5563,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>22</v>
@@ -5580,16 +5583,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>84</v>
@@ -5600,16 +5603,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>87</v>
@@ -5620,16 +5623,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>91</v>
@@ -5640,16 +5643,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>4</v>
@@ -5660,16 +5663,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>410</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>11</v>
@@ -5680,16 +5683,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>15</v>
@@ -5700,16 +5703,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>18</v>
@@ -5720,16 +5723,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>22</v>
@@ -5740,16 +5743,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>84</v>
@@ -5760,16 +5763,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>87</v>
@@ -5780,16 +5783,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>4</v>
@@ -5800,16 +5803,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>8</v>
@@ -5820,16 +5823,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>11</v>
@@ -5840,16 +5843,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>15</v>
@@ -5860,16 +5863,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>18</v>
@@ -5880,16 +5883,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>22</v>
@@ -5900,16 +5903,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>4</v>
@@ -5920,16 +5923,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>438</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>8</v>
@@ -5940,16 +5943,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>11</v>
@@ -5960,16 +5963,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>15</v>
@@ -5980,16 +5983,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>18</v>
@@ -6000,16 +6003,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>22</v>
@@ -6020,16 +6023,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>4</v>
@@ -6040,16 +6043,16 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>451</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>8</v>
@@ -6060,16 +6063,16 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>11</v>
@@ -6080,16 +6083,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>15</v>
@@ -6100,16 +6103,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>18</v>
@@ -6120,16 +6123,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>22</v>
@@ -6140,16 +6143,16 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>84</v>
@@ -6160,16 +6163,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>4</v>
@@ -6180,16 +6183,16 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>8</v>
@@ -6200,16 +6203,16 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>11</v>
@@ -6220,16 +6223,16 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>15</v>
@@ -6240,16 +6243,16 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>18</v>
@@ -6260,16 +6263,16 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>22</v>
@@ -6280,16 +6283,16 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>84</v>
@@ -6300,16 +6303,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>4</v>
@@ -6320,16 +6323,16 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>481</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>8</v>
@@ -6340,16 +6343,16 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>11</v>
@@ -6360,16 +6363,16 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>15</v>
@@ -6380,16 +6383,16 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>18</v>
@@ -6400,16 +6403,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>22</v>
@@ -6420,16 +6423,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>84</v>
@@ -6440,16 +6443,16 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>87</v>
@@ -6460,16 +6463,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>4</v>
@@ -6480,16 +6483,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D227" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D227" s="1" t="s">
-        <v>498</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>8</v>
@@ -6500,16 +6503,16 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>11</v>
@@ -6520,16 +6523,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>15</v>
@@ -6540,16 +6543,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>18</v>
@@ -6560,16 +6563,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>22</v>
@@ -6580,16 +6583,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>84</v>
@@ -6600,16 +6603,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>87</v>
@@ -6620,16 +6623,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>91</v>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,21 +11,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="517">
   <si>
     <t/>
   </si>
   <si>
+    <t>20097776</t>
+  </si>
+  <si>
+    <t>JAPOTA HNY BUTTER 68</t>
+  </si>
+  <si>
+    <t>SNK06D</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
     <t>20136745</t>
   </si>
   <si>
     <t>JAPOTA PTATO ORI 68G</t>
   </si>
   <si>
-    <t>SNK06D</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>2</t>
   </si>
   <si>
     <t>RT,(E-14H)</t>
@@ -37,7 +49,7 @@
     <t>JAPOTA BEEF BBQ 68G</t>
   </si>
   <si>
-    <t>2</t>
+    <t>3</t>
   </si>
   <si>
     <t>20125580</t>
@@ -46,10 +58,31 @@
     <t>JAPOTA NPS PDS 68G</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20094328</t>
+  </si>
+  <si>
+    <t>PIATTOS SMB GPREK 65</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20097774</t>
+  </si>
+  <si>
+    <t>JAPOTA JPN.SEAWD 68G</t>
+  </si>
+  <si>
+    <t>20131098</t>
+  </si>
+  <si>
+    <t>POTABEE SPICY BBQ 65</t>
   </si>
   <si>
     <t>20093941</t>
@@ -58,19 +91,496 @@
     <t>POTABEE AYM BKR 65G</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20094328</t>
-  </si>
-  <si>
-    <t>PIATTOS SMB GPREK 65</t>
+    <t>20071780</t>
+  </si>
+  <si>
+    <t>POTABEE CHIP BBQ 65G</t>
+  </si>
+  <si>
+    <t>20071781</t>
+  </si>
+  <si>
+    <t>POTABEE CHIP SWD 65G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
+    <t>20025762</t>
+  </si>
+  <si>
+    <t>PIATTOS SAPI PNG 65G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20132750</t>
+  </si>
+  <si>
+    <t>CHITATO AYAM BWG 65G</t>
+  </si>
+  <si>
+    <t>20116686</t>
+  </si>
+  <si>
+    <t>CHTATO LITE C/ONN 68</t>
+  </si>
+  <si>
+    <t>20131037</t>
+  </si>
+  <si>
+    <t>CHTATOLITE ABR.SWD65</t>
+  </si>
+  <si>
+    <t>20138228</t>
+  </si>
+  <si>
+    <t>LAYS RUMPUT LAUT 64G</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20138229</t>
+  </si>
+  <si>
+    <t>LAYS DGG SAPI BKR64G</t>
+  </si>
+  <si>
+    <t>20141504</t>
+  </si>
+  <si>
+    <t>LAYS RMPT LAUT PDS64</t>
+  </si>
+  <si>
+    <t>20116670</t>
+  </si>
+  <si>
+    <t>CHTATO LITE NORI 65G</t>
+  </si>
+  <si>
+    <t>20116684</t>
+  </si>
+  <si>
+    <t>CHTATO LITE SLMON 68</t>
+  </si>
+  <si>
+    <t>20139713</t>
+  </si>
+  <si>
+    <t>CHITATO BEEF MALA 65</t>
+  </si>
+  <si>
+    <t>20136744</t>
+  </si>
+  <si>
+    <t>CHITATO TTEOK-BK 65G</t>
+  </si>
+  <si>
+    <t>20141944</t>
+  </si>
+  <si>
+    <t>CHITATO RNDG SAPI 62</t>
+  </si>
+  <si>
+    <t>10001094</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PGG 65G</t>
+  </si>
+  <si>
+    <t>20122264</t>
+  </si>
+  <si>
+    <t>CHITATO MI GORENG 65</t>
+  </si>
+  <si>
+    <t>10001093</t>
+  </si>
+  <si>
+    <t>CHITATO AYAM BMB 65G</t>
+  </si>
+  <si>
+    <t>20014506</t>
+  </si>
+  <si>
+    <t>CHITATO CHEESE SPR65</t>
+  </si>
+  <si>
+    <t>20023435</t>
+  </si>
+  <si>
+    <t>CHITATO SP BMB BKR65</t>
+  </si>
+  <si>
+    <t>20029228</t>
+  </si>
+  <si>
+    <t>CHITATO AYAM BBQ 65G</t>
+  </si>
+  <si>
+    <t>20052859</t>
+  </si>
+  <si>
+    <t>PRINGLES ORIGINAL 42</t>
+  </si>
+  <si>
+    <t>20111009</t>
+  </si>
+  <si>
+    <t>PRINGLES CHSY CHS 42</t>
+  </si>
+  <si>
+    <t>20052860</t>
+  </si>
+  <si>
+    <t>PRINGLES SOURS CRM42</t>
+  </si>
+  <si>
+    <t>20129961</t>
+  </si>
+  <si>
+    <t>MR.POTATO ORG KLG 35</t>
+  </si>
+  <si>
+    <t>20106307</t>
+  </si>
+  <si>
+    <t>MR.POTATO GHOST/P 40</t>
+  </si>
+  <si>
+    <t>20120198</t>
+  </si>
+  <si>
+    <t>MR/P GHST/P SWEED40</t>
+  </si>
+  <si>
+    <t>20141098</t>
+  </si>
+  <si>
+    <t>MR PTT BULDAK CHES40</t>
+  </si>
+  <si>
+    <t>20139841</t>
+  </si>
+  <si>
+    <t>MR POTATO CRBNARA 40</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139544</t>
+  </si>
+  <si>
+    <t>LAYS STAX SOUR&amp;O 70G</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20139536</t>
+  </si>
+  <si>
+    <t>LAYS STAX ORGNL 70G</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20023846</t>
+  </si>
+  <si>
+    <t>PRNGLES ORIGNAL 102G</t>
+  </si>
+  <si>
+    <t>20023845</t>
+  </si>
+  <si>
+    <t>PRINGLES CHEESY 102G</t>
+  </si>
+  <si>
+    <t>20044093</t>
+  </si>
+  <si>
+    <t>PRNGLES S.CRM&amp;O 102G</t>
+  </si>
+  <si>
+    <t>20141457</t>
+  </si>
+  <si>
+    <t>PRLGS BR SWD 102</t>
+  </si>
+  <si>
+    <t>RT,(E-27H)</t>
+  </si>
+  <si>
+    <t>20136007</t>
+  </si>
+  <si>
+    <t>MR.POTATO BBQ 85G</t>
+  </si>
+  <si>
+    <t>20135539</t>
+  </si>
+  <si>
+    <t>MR.POTATO ORGINAL85G</t>
+  </si>
+  <si>
+    <t>20135538</t>
+  </si>
+  <si>
+    <t>MR.POTATO SOUR&amp;O 85G</t>
+  </si>
+  <si>
+    <t>20137054</t>
+  </si>
+  <si>
+    <t>CHTATO LITE ASLI 110</t>
+  </si>
+  <si>
+    <t>20137572</t>
+  </si>
+  <si>
+    <t>CHTATO LITE KEJU 110</t>
+  </si>
+  <si>
+    <t>10000739</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PANG.35</t>
+  </si>
+  <si>
+    <t>20092063</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PGG 115</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20002987</t>
+  </si>
+  <si>
+    <t>KUSUKA KRP BARBQU 60</t>
+  </si>
+  <si>
+    <t>20002988</t>
+  </si>
+  <si>
+    <t>KUSUKA KRP AYM LD 60</t>
+  </si>
+  <si>
+    <t>20026343</t>
+  </si>
+  <si>
+    <t>KUSUKA RMPT LAUT 60</t>
+  </si>
+  <si>
+    <t>20056958</t>
+  </si>
+  <si>
+    <t>QTELA TEMPE R/LAUT55</t>
+  </si>
+  <si>
+    <t>20033450</t>
+  </si>
+  <si>
+    <t>QTELA KRP/TMPE ORI55</t>
+  </si>
+  <si>
+    <t>20045104</t>
+  </si>
+  <si>
+    <t>QTELA TEMPE CABE/R55</t>
+  </si>
+  <si>
+    <t>20137014</t>
+  </si>
+  <si>
+    <t>CHIMI KRP CHS.BR 41G</t>
+  </si>
+  <si>
+    <t>20131047</t>
+  </si>
+  <si>
+    <t>CHIMI KR.MENTEGA 41</t>
+  </si>
+  <si>
+    <t>20104728</t>
+  </si>
+  <si>
+    <t>CHIMI KRP.UB JG.BK41</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20104729</t>
+  </si>
+  <si>
+    <t>CHIMI KRP.UB JG.BL41</t>
+  </si>
+  <si>
+    <t>20021032</t>
+  </si>
+  <si>
+    <t>QTELA KERIPIK BLD 60</t>
+  </si>
+  <si>
+    <t>20012678</t>
+  </si>
+  <si>
+    <t>QTELA KERIPIK ORG 60</t>
+  </si>
+  <si>
+    <t>20012679</t>
+  </si>
+  <si>
+    <t>QTELA KRIPIK BBQ 60</t>
+  </si>
+  <si>
+    <t>20115362</t>
+  </si>
+  <si>
+    <t>CHUBA KRP BALADO 125</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20115363</t>
+  </si>
+  <si>
+    <t>CHUBA KRPK BBQ 125G</t>
+  </si>
+  <si>
+    <t>20137973</t>
+  </si>
+  <si>
+    <t>CHUBA KRIPIK KEJU125</t>
+  </si>
+  <si>
+    <t>20093110</t>
+  </si>
+  <si>
+    <t>KUSUKA BALADO 180G</t>
+  </si>
+  <si>
+    <t>20000516</t>
+  </si>
+  <si>
+    <t>KUSUKA KRPK BBQ 180</t>
+  </si>
+  <si>
+    <t>20021029</t>
+  </si>
+  <si>
+    <t>QTELA KRPK BLDO 175G</t>
+  </si>
+  <si>
+    <t>20012681</t>
+  </si>
+  <si>
+    <t>QTELA KRIPIK BBQ 175</t>
+  </si>
+  <si>
+    <t>20128427</t>
+  </si>
+  <si>
+    <t>QTELA KS RP.LAUT 100</t>
+  </si>
+  <si>
+    <t>20124903</t>
+  </si>
+  <si>
+    <t>QTELA KR AY LD/HT100</t>
+  </si>
+  <si>
+    <t>20093109</t>
+  </si>
+  <si>
+    <t>KUSUKA ORIGINAL 180G</t>
+  </si>
+  <si>
+    <t>20012680</t>
+  </si>
+  <si>
+    <t>QTELA KRPK ORG 175G</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20140882</t>
+  </si>
+  <si>
+    <t>LAYS WAVY SAPI 105G</t>
+  </si>
+  <si>
+    <t>20122571</t>
+  </si>
+  <si>
+    <t>PIATTOS SAPI PG 115G</t>
+  </si>
+  <si>
+    <t>20134572</t>
+  </si>
+  <si>
+    <t>PIATTOS SMB GPRK 115</t>
+  </si>
+  <si>
+    <t>20119437</t>
+  </si>
+  <si>
+    <t>POTABEE BBG 115G</t>
+  </si>
+  <si>
+    <t>20116675</t>
+  </si>
+  <si>
+    <t>CHTATO LITE NORI 115</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20139538</t>
+  </si>
+  <si>
+    <t>LAYS RMPT LAUT 105G</t>
+  </si>
+  <si>
+    <t>20134456</t>
+  </si>
+  <si>
+    <t>JAPOTA SEAWEED 115G</t>
+  </si>
+  <si>
+    <t>20138949</t>
+  </si>
+  <si>
+    <t>JAPOTA H.HNY BTR 115</t>
+  </si>
+  <si>
+    <t>20119460</t>
+  </si>
+  <si>
+    <t>POTABEE SEAWEED 115G</t>
+  </si>
+  <si>
+    <t>20137778</t>
+  </si>
+  <si>
+    <t>CHIMI JG.BKR 85G</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>20131518</t>
@@ -79,505 +589,505 @@
     <t>KSUKA KRP KR.AYM 100</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20097774</t>
-  </si>
-  <si>
-    <t>JAPOTA JPN.SEAWD 68G</t>
-  </si>
-  <si>
-    <t>20097776</t>
-  </si>
-  <si>
-    <t>JAPOTA HNY BUTTER 68</t>
-  </si>
-  <si>
-    <t>20131098</t>
-  </si>
-  <si>
-    <t>POTABEE SPICY BBQ 65</t>
-  </si>
-  <si>
-    <t>20071781</t>
-  </si>
-  <si>
-    <t>POTABEE CHIP SWD 65G</t>
-  </si>
-  <si>
-    <t>20071780</t>
-  </si>
-  <si>
-    <t>POTABEE CHIP BBQ 65G</t>
-  </si>
-  <si>
-    <t>20025762</t>
-  </si>
-  <si>
-    <t>PIATTOS SAPI PNG 65G</t>
-  </si>
-  <si>
-    <t>20138228</t>
-  </si>
-  <si>
-    <t>LAYS RUMPUT LAUT 64G</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138229</t>
-  </si>
-  <si>
-    <t>LAYS DGG SAPI BKR64G</t>
-  </si>
-  <si>
-    <t>20141504</t>
-  </si>
-  <si>
-    <t>LAYS RMPT LAUT PDS64</t>
-  </si>
-  <si>
-    <t>20132750</t>
-  </si>
-  <si>
-    <t>CHITATO AYAM BWG 65G</t>
-  </si>
-  <si>
-    <t>20131037</t>
-  </si>
-  <si>
-    <t>CHTATOLITE ABR.SWD65</t>
-  </si>
-  <si>
-    <t>20116670</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 65G</t>
-  </si>
-  <si>
-    <t>20116684</t>
-  </si>
-  <si>
-    <t>CHTATO LITE SLMON 68</t>
-  </si>
-  <si>
-    <t>20116686</t>
-  </si>
-  <si>
-    <t>CHTATO LITE C/ONN 68</t>
-  </si>
-  <si>
-    <t>20139713</t>
-  </si>
-  <si>
-    <t>CHITATO BEEF MALA 65</t>
-  </si>
-  <si>
-    <t>20136744</t>
-  </si>
-  <si>
-    <t>CHITATO TTEOK-BK 65G</t>
-  </si>
-  <si>
-    <t>20141944</t>
-  </si>
-  <si>
-    <t>CHITATO RNDG SAPI 62</t>
-  </si>
-  <si>
-    <t>10001094</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 65G</t>
-  </si>
-  <si>
-    <t>20122264</t>
-  </si>
-  <si>
-    <t>CHITATO MI GORENG 65</t>
-  </si>
-  <si>
-    <t>10001093</t>
-  </si>
-  <si>
-    <t>CHITATO AYAM BMB 65G</t>
-  </si>
-  <si>
-    <t>20014506</t>
-  </si>
-  <si>
-    <t>CHITATO CHEESE SPR65</t>
-  </si>
-  <si>
-    <t>20023435</t>
-  </si>
-  <si>
-    <t>CHITATO SP BMB BKR65</t>
-  </si>
-  <si>
-    <t>20029228</t>
-  </si>
-  <si>
-    <t>CHITATO AYAM BBQ 65G</t>
-  </si>
-  <si>
-    <t>20052859</t>
-  </si>
-  <si>
-    <t>PRINGLES ORIGINAL 42</t>
-  </si>
-  <si>
-    <t>20111009</t>
-  </si>
-  <si>
-    <t>PRINGLES CHSY CHS 42</t>
-  </si>
-  <si>
-    <t>20052860</t>
-  </si>
-  <si>
-    <t>PRINGLES SOURS CRM42</t>
-  </si>
-  <si>
-    <t>20129961</t>
-  </si>
-  <si>
-    <t>MR.POTATO ORG KLG 35</t>
-  </si>
-  <si>
-    <t>20106307</t>
-  </si>
-  <si>
-    <t>MR.POTATO GHOST/P 40</t>
-  </si>
-  <si>
-    <t>20120198</t>
-  </si>
-  <si>
-    <t>MR/P GHST/P SWEED40</t>
-  </si>
-  <si>
-    <t>20141098</t>
-  </si>
-  <si>
-    <t>MR PTT BULDAK CHES40</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20139841</t>
-  </si>
-  <si>
-    <t>MR POTATO CRBNARA 40</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139544</t>
-  </si>
-  <si>
-    <t>LAYS STAX SOUR&amp;O 70G</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20139536</t>
-  </si>
-  <si>
-    <t>LAYS STAX ORGNL 70G</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20023846</t>
-  </si>
-  <si>
-    <t>PRNGLES ORIGNAL 102G</t>
-  </si>
-  <si>
-    <t>20023845</t>
-  </si>
-  <si>
-    <t>PRINGLES CHEESY 102G</t>
-  </si>
-  <si>
-    <t>20044093</t>
-  </si>
-  <si>
-    <t>PRNGLES S.CRM&amp;O 102G</t>
-  </si>
-  <si>
-    <t>20141457</t>
-  </si>
-  <si>
-    <t>PRLGS BR SWD 102</t>
-  </si>
-  <si>
-    <t>RT,(E-27H)</t>
-  </si>
-  <si>
-    <t>20136007</t>
-  </si>
-  <si>
-    <t>MR.POTATO BBQ 85G</t>
-  </si>
-  <si>
-    <t>20135539</t>
-  </si>
-  <si>
-    <t>MR.POTATO ORGINAL85G</t>
-  </si>
-  <si>
-    <t>20135538</t>
-  </si>
-  <si>
-    <t>MR.POTATO SOUR&amp;O 85G</t>
-  </si>
-  <si>
-    <t>20137054</t>
-  </si>
-  <si>
-    <t>CHTATO LITE ASLI 110</t>
-  </si>
-  <si>
-    <t>20137572</t>
-  </si>
-  <si>
-    <t>CHTATO LITE KEJU 110</t>
-  </si>
-  <si>
-    <t>10000739</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PANG.35</t>
-  </si>
-  <si>
-    <t>20092063</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 115</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20002987</t>
-  </si>
-  <si>
-    <t>KUSUKA KRP BARBQU 60</t>
-  </si>
-  <si>
-    <t>20002988</t>
-  </si>
-  <si>
-    <t>KUSUKA KRP AYM LD 60</t>
-  </si>
-  <si>
-    <t>20026343</t>
-  </si>
-  <si>
-    <t>KUSUKA RMPT LAUT 60</t>
-  </si>
-  <si>
-    <t>20056958</t>
-  </si>
-  <si>
-    <t>QTELA TEMPE R/LAUT55</t>
-  </si>
-  <si>
-    <t>20033450</t>
-  </si>
-  <si>
-    <t>QTELA KRP/TMPE ORI55</t>
-  </si>
-  <si>
-    <t>20045104</t>
-  </si>
-  <si>
-    <t>QTELA TEMPE CABE/R55</t>
-  </si>
-  <si>
-    <t>20137014</t>
-  </si>
-  <si>
-    <t>CHIMI KRP CHS.BR 41G</t>
-  </si>
-  <si>
-    <t>20131047</t>
-  </si>
-  <si>
-    <t>CHIMI KR.MENTEGA 41</t>
-  </si>
-  <si>
-    <t>20104728</t>
-  </si>
-  <si>
-    <t>CHIMI KRP.UB JG.BK41</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20104729</t>
-  </si>
-  <si>
-    <t>CHIMI KRP.UB JG.BL41</t>
-  </si>
-  <si>
-    <t>20021032</t>
-  </si>
-  <si>
-    <t>QTELA KERIPIK BLD 60</t>
-  </si>
-  <si>
-    <t>20012678</t>
-  </si>
-  <si>
-    <t>QTELA KERIPIK ORG 60</t>
-  </si>
-  <si>
-    <t>20012679</t>
-  </si>
-  <si>
-    <t>QTELA KRIPIK BBQ 60</t>
-  </si>
-  <si>
-    <t>20137778</t>
-  </si>
-  <si>
-    <t>CHIMI JG.BKR 85G</t>
-  </si>
-  <si>
-    <t>20115362</t>
-  </si>
-  <si>
-    <t>CHUBA KRP BALADO 125</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20115363</t>
-  </si>
-  <si>
-    <t>CHUBA KRPK BBQ 125G</t>
-  </si>
-  <si>
-    <t>20093110</t>
-  </si>
-  <si>
-    <t>KUSUKA BALADO 180G</t>
-  </si>
-  <si>
-    <t>20000516</t>
-  </si>
-  <si>
-    <t>KUSUKA KRPK BBQ 180</t>
-  </si>
-  <si>
-    <t>20021029</t>
-  </si>
-  <si>
-    <t>QTELA KRPK BLDO 175G</t>
-  </si>
-  <si>
-    <t>20012681</t>
-  </si>
-  <si>
-    <t>QTELA KRIPIK BBQ 175</t>
-  </si>
-  <si>
-    <t>20128427</t>
-  </si>
-  <si>
-    <t>QTELA KS RP.LAUT 100</t>
-  </si>
-  <si>
-    <t>20124903</t>
-  </si>
-  <si>
-    <t>QTELA KR AY LD/HT100</t>
-  </si>
-  <si>
-    <t>20093109</t>
-  </si>
-  <si>
-    <t>KUSUKA ORIGINAL 180G</t>
-  </si>
-  <si>
-    <t>20012680</t>
-  </si>
-  <si>
-    <t>QTELA KRPK ORG 175G</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20140882</t>
-  </si>
-  <si>
-    <t>LAYS WAVY SAPI 105G</t>
-  </si>
-  <si>
-    <t>20122571</t>
-  </si>
-  <si>
-    <t>PIATTOS SAPI PG 115G</t>
-  </si>
-  <si>
-    <t>20134572</t>
-  </si>
-  <si>
-    <t>PIATTOS SMB GPRK 115</t>
-  </si>
-  <si>
-    <t>20119437</t>
-  </si>
-  <si>
-    <t>POTABEE BBG 115G</t>
-  </si>
-  <si>
-    <t>20116675</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 115</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20139538</t>
-  </si>
-  <si>
-    <t>LAYS RMPT LAUT 105G</t>
-  </si>
-  <si>
-    <t>20134456</t>
-  </si>
-  <si>
-    <t>JAPOTA SEAWEED 115G</t>
-  </si>
-  <si>
-    <t>20138949</t>
-  </si>
-  <si>
-    <t>JAPOTA H.HNY BTR 115</t>
-  </si>
-  <si>
-    <t>20119460</t>
-  </si>
-  <si>
-    <t>POTABEE SEAWEED 115G</t>
+    <t>20078113</t>
+  </si>
+  <si>
+    <t>POPPY POP JGG BKR 60</t>
+  </si>
+  <si>
+    <t>20049993</t>
+  </si>
+  <si>
+    <t>SUKY2 SNCK UDG MNS60</t>
+  </si>
+  <si>
+    <t>20034684</t>
+  </si>
+  <si>
+    <t>KRAKER UDANG PDS 60</t>
+  </si>
+  <si>
+    <t>20004229</t>
+  </si>
+  <si>
+    <t>SMAX RING CHEESE 40G</t>
+  </si>
+  <si>
+    <t>20110634</t>
+  </si>
+  <si>
+    <t>GARUDA O'CORN SS 70G</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20124707</t>
+  </si>
+  <si>
+    <t>GRD O'CORN JG/BKR 70</t>
+  </si>
+  <si>
+    <t>20139291</t>
+  </si>
+  <si>
+    <t>FLOATY SNACK BWNG 60</t>
+  </si>
+  <si>
+    <t>20140056</t>
+  </si>
+  <si>
+    <t>FLOATY TERSERAH 60G</t>
+  </si>
+  <si>
+    <t>20141100</t>
+  </si>
+  <si>
+    <t>WONHAE BANANA MB 60G</t>
+  </si>
+  <si>
+    <t>20116109</t>
+  </si>
+  <si>
+    <t>MXCORN ROAST.CR 55G</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20083529</t>
+  </si>
+  <si>
+    <t>HAPPY TOS SEAWEED 52</t>
+  </si>
+  <si>
+    <t>20037179</t>
+  </si>
+  <si>
+    <t>HAPPYTOS CHP R.CRN55</t>
+  </si>
+  <si>
+    <t>20138599</t>
+  </si>
+  <si>
+    <t>JETZ TOR JG.BKR 140G</t>
+  </si>
+  <si>
+    <t>20130447</t>
+  </si>
+  <si>
+    <t>TOS TOS TRTCS RC140</t>
+  </si>
+  <si>
+    <t>20128517</t>
+  </si>
+  <si>
+    <t>TOS TOS TRTCS KB140</t>
+  </si>
+  <si>
+    <t>20138231</t>
+  </si>
+  <si>
+    <t>DORITOS SMB SALSA120</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20138230</t>
+  </si>
+  <si>
+    <t>DORITOS JGG BKR 120G</t>
+  </si>
+  <si>
+    <t>20142266</t>
+  </si>
+  <si>
+    <t>DORITOS NCHO CHS 120</t>
+  </si>
+  <si>
+    <t>20131013</t>
+  </si>
+  <si>
+    <t>PANCHOS CABE PDS 145</t>
+  </si>
+  <si>
+    <t>20119019</t>
+  </si>
+  <si>
+    <t>HAPPYTOS HOT CHL 140</t>
+  </si>
+  <si>
+    <t>20072195</t>
+  </si>
+  <si>
+    <t>MH MAITOS JG.BBQ 140</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20072194</t>
+  </si>
+  <si>
+    <t>MH MAITOS S.BLDO 140</t>
+  </si>
+  <si>
+    <t>20099956</t>
+  </si>
+  <si>
+    <t>PANCHOS PEDAS 140G</t>
+  </si>
+  <si>
+    <t>20099955</t>
+  </si>
+  <si>
+    <t>PANCHOS SAPI.PG 140G</t>
+  </si>
+  <si>
+    <t>20098166</t>
+  </si>
+  <si>
+    <t>HAPPYTOS JG.BKR 140</t>
+  </si>
+  <si>
+    <t>20070033</t>
+  </si>
+  <si>
+    <t>HAPPYTOS NC.CHS 140G</t>
+  </si>
+  <si>
+    <t>20116112</t>
+  </si>
+  <si>
+    <t>MAXICORN BBQ 130G</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20116110</t>
+  </si>
+  <si>
+    <t>MXCORN ROAST.CR 130G</t>
+  </si>
+  <si>
+    <t>20116125</t>
+  </si>
+  <si>
+    <t>MXCORN NCHO CHS 130G</t>
+  </si>
+  <si>
+    <t>10002101</t>
+  </si>
+  <si>
+    <t>HAPPYTOS CHIP MRH140</t>
+  </si>
+  <si>
+    <t>10036957</t>
+  </si>
+  <si>
+    <t>HAPPYTOS CHIP HJU140</t>
+  </si>
+  <si>
+    <t>20104942</t>
+  </si>
+  <si>
+    <t>CHIKI BALL CHOCO 50G</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20116411</t>
+  </si>
+  <si>
+    <t>CHIKI PUFFS CHSE 60G</t>
+  </si>
+  <si>
+    <t>20101064</t>
+  </si>
+  <si>
+    <t>CHIKI BALL CHEESE 50</t>
+  </si>
+  <si>
+    <t>20101065</t>
+  </si>
+  <si>
+    <t>CHIKI BALL CHKN 50</t>
+  </si>
+  <si>
+    <t>20140251</t>
+  </si>
+  <si>
+    <t>CHIKI P/C SALT CRM72</t>
+  </si>
+  <si>
+    <t>20140264</t>
+  </si>
+  <si>
+    <t>CHIKI NUTTY CRML 50G</t>
+  </si>
+  <si>
+    <t>RT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20142265</t>
+  </si>
+  <si>
+    <t>WONHAE TPKI CHS BU80</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20132657</t>
+  </si>
+  <si>
+    <t>WONHAE TPKI CRM.RS80</t>
+  </si>
+  <si>
+    <t>20139930</t>
+  </si>
+  <si>
+    <t>WONHAE TPKI CHS TR80</t>
+  </si>
+  <si>
+    <t>20116410</t>
+  </si>
+  <si>
+    <t>CHIKI TWIST CORN 75G</t>
+  </si>
+  <si>
+    <t>20016624</t>
+  </si>
+  <si>
+    <t>STT FRENCH FRIES 24G</t>
+  </si>
+  <si>
+    <t>20125389</t>
+  </si>
+  <si>
+    <t>STT FRCH FRS LVL3 60</t>
+  </si>
+  <si>
+    <t>20034682</t>
+  </si>
+  <si>
+    <t>RIN-BEE STICK KEJU60</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20057730</t>
+  </si>
+  <si>
+    <t>TIC TIC STCK BWNG 70</t>
+  </si>
+  <si>
+    <t>20103371</t>
+  </si>
+  <si>
+    <t>TIC TIC STK BWG+SS65</t>
+  </si>
+  <si>
+    <t>20072575</t>
+  </si>
+  <si>
+    <t>KRISBEE F.FRIES 65G</t>
+  </si>
+  <si>
+    <t>20024699</t>
+  </si>
+  <si>
+    <t>STT FRENCH FRIES 62G</t>
+  </si>
+  <si>
+    <t>20138241</t>
+  </si>
+  <si>
+    <t>CHEETOS KEJU 120G</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20140272</t>
+  </si>
+  <si>
+    <t>CHIKI TWIST CORN 120</t>
+  </si>
+  <si>
+    <t>20132876</t>
+  </si>
+  <si>
+    <t>OISHIT THIN TRUFF100</t>
+  </si>
+  <si>
+    <t>20140085</t>
+  </si>
+  <si>
+    <t>O/TATER THIN SWD 100</t>
+  </si>
+  <si>
+    <t>20138236</t>
+  </si>
+  <si>
+    <t>CHEETOS JGG BKR 120G</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20134273</t>
+  </si>
+  <si>
+    <t>POPPY POP JGG BKR130</t>
+  </si>
+  <si>
+    <t>20092858</t>
+  </si>
+  <si>
+    <t>TWISTKO JGNG BKR 145</t>
+  </si>
+  <si>
+    <t>20133064</t>
+  </si>
+  <si>
+    <t>KRAKER UDANG PDS 130</t>
+  </si>
+  <si>
+    <t>20138106</t>
+  </si>
+  <si>
+    <t>TIC TIC STCK BWG 135</t>
+  </si>
+  <si>
+    <t>20092857</t>
+  </si>
+  <si>
+    <t>STT FRENCH FRIES 130</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20119036</t>
+  </si>
+  <si>
+    <t>RIN-BEE STK KJU 130G</t>
+  </si>
+  <si>
+    <t>20126424</t>
+  </si>
+  <si>
+    <t>TARO SEAWEED 115G</t>
+  </si>
+  <si>
+    <t>20120421</t>
+  </si>
+  <si>
+    <t>TARO POTATO BBQ 115G</t>
+  </si>
+  <si>
+    <t>20101933</t>
+  </si>
+  <si>
+    <t>CHIKI BALL CHOC 200G</t>
+  </si>
+  <si>
+    <t>20117923</t>
+  </si>
+  <si>
+    <t>T K NOI S/LVR ORI2'S</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20117928</t>
+  </si>
+  <si>
+    <t>T K NOI S/LVR SPCY2S</t>
+  </si>
+  <si>
+    <t>20072581</t>
+  </si>
+  <si>
+    <t>IDM SEAWEED ORG 20G</t>
+  </si>
+  <si>
+    <t>20072582</t>
+  </si>
+  <si>
+    <t>IDM SEAWEED BBQ 20G</t>
+  </si>
+  <si>
+    <t>20022707</t>
+  </si>
+  <si>
+    <t>TAO KAE CRSPY ORG 15</t>
+  </si>
+  <si>
+    <t>20024856</t>
+  </si>
+  <si>
+    <t>TAO KAE CLASSIC 3.2G</t>
+  </si>
+  <si>
+    <t>20042370</t>
+  </si>
+  <si>
+    <t>M/SUKA R/LAUT PNG 9G</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20097390</t>
+  </si>
+  <si>
+    <t>M/SUKA NORI BBQ2X4.5</t>
+  </si>
+  <si>
+    <t>20073871</t>
+  </si>
+  <si>
+    <t>M/SUKA NORI PDS2X4.5</t>
+  </si>
+  <si>
+    <t>20097391</t>
+  </si>
+  <si>
+    <t>M/SK NORI S.EGG2X4.5</t>
+  </si>
+  <si>
+    <t>20118737</t>
+  </si>
+  <si>
+    <t>M/SK NORI J.BKR2X4.5</t>
+  </si>
+  <si>
+    <t>20138203</t>
+  </si>
+  <si>
+    <t>M/SK GIM BORI BIG 3G</t>
+  </si>
+  <si>
+    <t>10006890</t>
+  </si>
+  <si>
+    <t>TWISTKO JGNG BKR 40G</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20064426</t>
+  </si>
+  <si>
+    <t>TWISTKO JGNG BKR 70G</t>
   </si>
   <si>
     <t>20112370</t>
@@ -586,9 +1096,6 @@
     <t>BC MKRONI LV.15 135G</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>20112444</t>
   </si>
   <si>
@@ -607,510 +1114,15 @@
     <t>DK RONI RS.CORN 135G</t>
   </si>
   <si>
-    <t>20049993</t>
-  </si>
-  <si>
-    <t>SUKY2 SNCK UDG MNS60</t>
-  </si>
-  <si>
-    <t>20034684</t>
-  </si>
-  <si>
-    <t>KRAKER UDANG PDS 60</t>
-  </si>
-  <si>
-    <t>20124707</t>
-  </si>
-  <si>
-    <t>GRD O'CORN JG/BKR 70</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20139291</t>
-  </si>
-  <si>
-    <t>FLOATY SNACK BWNG 60</t>
-  </si>
-  <si>
-    <t>20140056</t>
-  </si>
-  <si>
-    <t>FLOATY TERSERAH 60G</t>
-  </si>
-  <si>
-    <t>20078113</t>
-  </si>
-  <si>
-    <t>POPPY POP JGG BKR 60</t>
-  </si>
-  <si>
-    <t>20110634</t>
-  </si>
-  <si>
-    <t>GARUDA O'CORN SS 70G</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20116109</t>
-  </si>
-  <si>
-    <t>MXCORN ROAST.CR 55G</t>
-  </si>
-  <si>
-    <t>20083529</t>
-  </si>
-  <si>
-    <t>HAPPY TOS SEAWEED 52</t>
-  </si>
-  <si>
-    <t>20037179</t>
-  </si>
-  <si>
-    <t>HAPPYTOS CHP R.CRN55</t>
-  </si>
-  <si>
-    <t>20130447</t>
-  </si>
-  <si>
-    <t>TOS TOS TRTCS RC140</t>
-  </si>
-  <si>
-    <t>20128517</t>
-  </si>
-  <si>
-    <t>TOS TOS TRTCS KB140</t>
-  </si>
-  <si>
-    <t>20138231</t>
-  </si>
-  <si>
-    <t>DORITOS SMB SALSA120</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20138230</t>
-  </si>
-  <si>
-    <t>DORITOS JGG BKR 120G</t>
-  </si>
-  <si>
-    <t>20142266</t>
-  </si>
-  <si>
-    <t>DORITOS NCHO CHS 120</t>
-  </si>
-  <si>
-    <t>20131013</t>
-  </si>
-  <si>
-    <t>PANCHOS CABE PDS 145</t>
-  </si>
-  <si>
-    <t>20138599</t>
-  </si>
-  <si>
-    <t>JETZ TOR JG.BKR 140G</t>
-  </si>
-  <si>
-    <t>20119019</t>
-  </si>
-  <si>
-    <t>HAPPYTOS HOT CHL 140</t>
-  </si>
-  <si>
-    <t>20072195</t>
-  </si>
-  <si>
-    <t>MH MAITOS JG.BBQ 140</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20072194</t>
-  </si>
-  <si>
-    <t>MH MAITOS S.BLDO 140</t>
-  </si>
-  <si>
-    <t>20099956</t>
-  </si>
-  <si>
-    <t>PANCHOS PEDAS 140G</t>
-  </si>
-  <si>
-    <t>20099955</t>
-  </si>
-  <si>
-    <t>PANCHOS SAPI.PG 140G</t>
-  </si>
-  <si>
-    <t>20098166</t>
-  </si>
-  <si>
-    <t>HAPPYTOS JG.BKR 140</t>
-  </si>
-  <si>
-    <t>20070033</t>
-  </si>
-  <si>
-    <t>HAPPYTOS NC.CHS 140G</t>
-  </si>
-  <si>
-    <t>20116112</t>
-  </si>
-  <si>
-    <t>MAXICORN BBQ 140G</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20116110</t>
-  </si>
-  <si>
-    <t>MXCORN ROAST.CR 140G</t>
-  </si>
-  <si>
-    <t>20116125</t>
-  </si>
-  <si>
-    <t>MXCORN NCHO CHS 140G</t>
-  </si>
-  <si>
-    <t>10002101</t>
-  </si>
-  <si>
-    <t>HAPPYTOS CHIP MRH140</t>
-  </si>
-  <si>
-    <t>10036957</t>
-  </si>
-  <si>
-    <t>HAPPYTOS CHIP HJU140</t>
-  </si>
-  <si>
-    <t>20104942</t>
-  </si>
-  <si>
-    <t>CHIKI BALL CHOCO 50G</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20116411</t>
-  </si>
-  <si>
-    <t>CHIKI PUFFS CHSE 60G</t>
-  </si>
-  <si>
-    <t>20101064</t>
-  </si>
-  <si>
-    <t>CHIKI BALL CHEESE 50</t>
-  </si>
-  <si>
-    <t>20101065</t>
-  </si>
-  <si>
-    <t>CHIKI BALL CHKN 50</t>
-  </si>
-  <si>
-    <t>20140251</t>
-  </si>
-  <si>
-    <t>CHIKI P/C SALT CRM72</t>
-  </si>
-  <si>
-    <t>20140264</t>
-  </si>
-  <si>
-    <t>CHIKI NUTTY CRML 50G</t>
-  </si>
-  <si>
-    <t>RT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20142265</t>
-  </si>
-  <si>
-    <t>WONHAE TPKI CHS BU80</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>,(E-1B)</t>
-  </si>
-  <si>
-    <t>20132657</t>
-  </si>
-  <si>
-    <t>WONHAE TPKI CRM.RS80</t>
-  </si>
-  <si>
-    <t>20139930</t>
-  </si>
-  <si>
-    <t>WONHAE TPKI CHS TR80</t>
-  </si>
-  <si>
-    <t>20141100</t>
-  </si>
-  <si>
-    <t>WONHAE BANANA MB 60G</t>
-  </si>
-  <si>
-    <t>20116410</t>
-  </si>
-  <si>
-    <t>CHIKI TWIST CORN 75G</t>
-  </si>
-  <si>
-    <t>20140272</t>
-  </si>
-  <si>
-    <t>CHIKI TWIST CORN 120</t>
-  </si>
-  <si>
-    <t>20034682</t>
-  </si>
-  <si>
-    <t>RIN-BEE STICK KEJU60</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20057730</t>
-  </si>
-  <si>
-    <t>TIC TIC STCK BWNG 70</t>
-  </si>
-  <si>
-    <t>20103371</t>
-  </si>
-  <si>
-    <t>TIC TIC STK BWG+SS65</t>
-  </si>
-  <si>
-    <t>20072575</t>
-  </si>
-  <si>
-    <t>KRISBEE F.FRIES 65G</t>
-  </si>
-  <si>
-    <t>20016624</t>
-  </si>
-  <si>
-    <t>STT FRENCH FRIES 24G</t>
-  </si>
-  <si>
-    <t>20125389</t>
-  </si>
-  <si>
-    <t>STT FRCH FRS LVL3 60</t>
-  </si>
-  <si>
-    <t>20138241</t>
-  </si>
-  <si>
-    <t>CHEETOS KEJU 120G</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20132876</t>
-  </si>
-  <si>
-    <t>OISHIT THIN TRUFF100</t>
-  </si>
-  <si>
-    <t>20140085</t>
-  </si>
-  <si>
-    <t>O/TATER THIN SWD 100</t>
-  </si>
-  <si>
-    <t>20024699</t>
-  </si>
-  <si>
-    <t>STT FRENCH FRIES 62G</t>
-  </si>
-  <si>
-    <t>20138236</t>
-  </si>
-  <si>
-    <t>CHEETOS JGG BKR 120G</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>20134273</t>
-  </si>
-  <si>
-    <t>POPPY POP JGG BKR130</t>
-  </si>
-  <si>
-    <t>20092858</t>
-  </si>
-  <si>
-    <t>TWISTKO JGNG BKR 145</t>
-  </si>
-  <si>
-    <t>20133064</t>
-  </si>
-  <si>
-    <t>KRAKER UDANG PDS 130</t>
-  </si>
-  <si>
-    <t>20138106</t>
-  </si>
-  <si>
-    <t>TIC TIC STCK BWG 135</t>
-  </si>
-  <si>
-    <t>20092857</t>
-  </si>
-  <si>
-    <t>STT FRENCH FRIES 130</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20119036</t>
-  </si>
-  <si>
-    <t>RIN-BEE STK KJU 130G</t>
-  </si>
-  <si>
-    <t>20126424</t>
-  </si>
-  <si>
-    <t>TARO SEAWEED 115G</t>
-  </si>
-  <si>
-    <t>20120421</t>
-  </si>
-  <si>
-    <t>TARO POTATO BBQ 115G</t>
-  </si>
-  <si>
-    <t>20101933</t>
-  </si>
-  <si>
-    <t>CHIKI BALL CHOC 200G</t>
-  </si>
-  <si>
-    <t>20117923</t>
-  </si>
-  <si>
-    <t>T K NOI S/LVR ORI2'S</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20022707</t>
-  </si>
-  <si>
-    <t>TAO KAE CRSPY ORG 15</t>
-  </si>
-  <si>
-    <t>20024856</t>
-  </si>
-  <si>
-    <t>TAO KAE CLASSIC 3.2G</t>
-  </si>
-  <si>
-    <t>20072581</t>
-  </si>
-  <si>
-    <t>IDM SEAWEED ORG 20G</t>
-  </si>
-  <si>
-    <t>20072582</t>
-  </si>
-  <si>
-    <t>IDM SEAWEED BBQ 20G</t>
-  </si>
-  <si>
-    <t>20138203</t>
-  </si>
-  <si>
-    <t>M/SK GIM BORI BIG 3G</t>
-  </si>
-  <si>
-    <t>20117928</t>
-  </si>
-  <si>
-    <t>T K NOI S/LVR SPCY2S</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20042370</t>
-  </si>
-  <si>
-    <t>M/SUKA R/LAUT PNG 9G</t>
-  </si>
-  <si>
-    <t>20097390</t>
-  </si>
-  <si>
-    <t>M/SUKA NORI BBQ2X4.5</t>
-  </si>
-  <si>
-    <t>20073871</t>
-  </si>
-  <si>
-    <t>M/SUKA NORI PDS2X4.5</t>
-  </si>
-  <si>
-    <t>20097391</t>
-  </si>
-  <si>
-    <t>M/SK NORI S.EGG2X4.5</t>
-  </si>
-  <si>
-    <t>20118737</t>
-  </si>
-  <si>
-    <t>M/SK NORI J.BKR2X4.5</t>
-  </si>
-  <si>
-    <t>20064426</t>
-  </si>
-  <si>
-    <t>TWISTKO JGNG BKR 70G</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>10006890</t>
-  </si>
-  <si>
-    <t>TWISTKO JGNG BKR 40G</t>
-  </si>
-  <si>
     <t>20114756</t>
   </si>
   <si>
     <t>GURIBEE BBQ BLDO 65G</t>
   </si>
   <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>20114757</t>
   </si>
   <si>
@@ -1129,7 +1141,115 @@
     <t>JETZ CROISANT CHOC50</t>
   </si>
   <si>
-    <t>29</t>
+    <t>20103852</t>
+  </si>
+  <si>
+    <t>JETZ CHOCOFIESTA 65G</t>
+  </si>
+  <si>
+    <t>10000752</t>
+  </si>
+  <si>
+    <t>TARO SNACK BARBQ 32G</t>
+  </si>
+  <si>
+    <t>20097777</t>
+  </si>
+  <si>
+    <t>KRISBEE PLW CHO 100G</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20081238</t>
+  </si>
+  <si>
+    <t>TARO NET TRYK BBQ 62</t>
+  </si>
+  <si>
+    <t>20055205</t>
+  </si>
+  <si>
+    <t>TARO SEAWEED 62G</t>
+  </si>
+  <si>
+    <t>20055204</t>
+  </si>
+  <si>
+    <t>TARO POTATO BBQ 62G</t>
+  </si>
+  <si>
+    <t>10000753</t>
+  </si>
+  <si>
+    <t>TARO SNACK SEAWED 32</t>
+  </si>
+  <si>
+    <t>20069696</t>
+  </si>
+  <si>
+    <t>OISHI POPCRN KRML100</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20069844</t>
+  </si>
+  <si>
+    <t>OISHI POPCRN COK 100</t>
+  </si>
+  <si>
+    <t>20125388</t>
+  </si>
+  <si>
+    <t>OISHI PCORN M/BLG100</t>
+  </si>
+  <si>
+    <t>20045784</t>
+  </si>
+  <si>
+    <t>OISHI SPNG/C CHO 100</t>
+  </si>
+  <si>
+    <t>20047335</t>
+  </si>
+  <si>
+    <t>OISHI SPNG STRW 100G</t>
+  </si>
+  <si>
+    <t>20136289</t>
+  </si>
+  <si>
+    <t>OISHI SPONGE UBI 100</t>
+  </si>
+  <si>
+    <t>20034686</t>
+  </si>
+  <si>
+    <t>OISHI PILLOW UBI 100</t>
+  </si>
+  <si>
+    <t>20034685</t>
+  </si>
+  <si>
+    <t>OISHI PILLOW CHO 100</t>
+  </si>
+  <si>
+    <t>20141746</t>
+  </si>
+  <si>
+    <t>OISHI PLLOW STRW 100</t>
+  </si>
+  <si>
+    <t>10027672</t>
+  </si>
+  <si>
+    <t>GERY SNCK SEREAL 100</t>
+  </si>
+  <si>
+    <t>32</t>
   </si>
   <si>
     <t>20139969</t>
@@ -1138,117 +1258,12 @@
     <t>GERY SNAK BANTAL 75G</t>
   </si>
   <si>
-    <t>20004229</t>
-  </si>
-  <si>
-    <t>SMAX RING CHEESE 40G</t>
-  </si>
-  <si>
-    <t>10000752</t>
-  </si>
-  <si>
-    <t>TARO SNACK BARBQ 32G</t>
-  </si>
-  <si>
-    <t>20097777</t>
-  </si>
-  <si>
-    <t>KRISBEE PLW CHO 100G</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20081238</t>
-  </si>
-  <si>
-    <t>TARO NET TRYK BBQ 62</t>
-  </si>
-  <si>
-    <t>20055205</t>
-  </si>
-  <si>
-    <t>TARO SEAWEED 62G</t>
-  </si>
-  <si>
-    <t>20055204</t>
-  </si>
-  <si>
-    <t>TARO POTATO BBQ 62G</t>
-  </si>
-  <si>
-    <t>10000753</t>
-  </si>
-  <si>
-    <t>TARO SNACK SEAWED 32</t>
-  </si>
-  <si>
-    <t>20069696</t>
-  </si>
-  <si>
-    <t>OISHI POPCRN KRML100</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20069844</t>
-  </si>
-  <si>
-    <t>OISHI POPCRN COK 100</t>
-  </si>
-  <si>
-    <t>20125388</t>
-  </si>
-  <si>
-    <t>OISHI PCORN M/BLG100</t>
-  </si>
-  <si>
-    <t>20045784</t>
-  </si>
-  <si>
-    <t>OISHI SPNG/C CHO 100</t>
-  </si>
-  <si>
-    <t>20047335</t>
-  </si>
-  <si>
-    <t>OISHI SPNG STRW 100G</t>
-  </si>
-  <si>
-    <t>20136289</t>
-  </si>
-  <si>
-    <t>OISHI SPONGE UBI 100</t>
-  </si>
-  <si>
-    <t>20034686</t>
-  </si>
-  <si>
-    <t>OISHI PILLOW UBI 100</t>
-  </si>
-  <si>
-    <t>20034685</t>
-  </si>
-  <si>
-    <t>OISHI PILLOW CHO 100</t>
-  </si>
-  <si>
-    <t>20141746</t>
-  </si>
-  <si>
-    <t>OISHI PLLOW STRW 100</t>
-  </si>
-  <si>
     <t>20036562</t>
   </si>
   <si>
     <t>S/N SOSIS AYAM 500</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
     <t>10024188</t>
   </si>
   <si>
@@ -1273,16 +1288,58 @@
     <t>MI GEMEZ SPICY 3X26G</t>
   </si>
   <si>
-    <t>10027672</t>
-  </si>
-  <si>
-    <t>GERY SNCK SEREAL 100</t>
-  </si>
-  <si>
-    <t>20103852</t>
-  </si>
-  <si>
-    <t>JETZ CHOCOFIESTA 65G</t>
+    <t>20127483</t>
+  </si>
+  <si>
+    <t>GRUDA PILUS RDNG 80</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20092875</t>
+  </si>
+  <si>
+    <t>GRUDA PILUS MI GR 80</t>
+  </si>
+  <si>
+    <t>20040528</t>
+  </si>
+  <si>
+    <t>TIC TAC MIX 80G</t>
+  </si>
+  <si>
+    <t>20132864</t>
+  </si>
+  <si>
+    <t>TIC TAC MIE GORENG80</t>
+  </si>
+  <si>
+    <t>20023148</t>
+  </si>
+  <si>
+    <t>TIC TAC SAPI PNGG 80</t>
+  </si>
+  <si>
+    <t>10000341</t>
+  </si>
+  <si>
+    <t>DUA KELINCI KCG 370G</t>
+  </si>
+  <si>
+    <t>10003422</t>
+  </si>
+  <si>
+    <t>GARUDA KC.GARING 350</t>
+  </si>
+  <si>
+    <t>10026500</t>
+  </si>
+  <si>
+    <t>DK KCNG BWNG PTH 180</t>
+  </si>
+  <si>
+    <t>34</t>
   </si>
   <si>
     <t>20007824</t>
@@ -1291,9 +1348,6 @@
     <t>D/K KCNG SANGRAI 180</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
     <t>10000348</t>
   </si>
   <si>
@@ -1312,57 +1366,6 @@
     <t>IDM KACANG KULIT 180</t>
   </si>
   <si>
-    <t>10000341</t>
-  </si>
-  <si>
-    <t>DUA KELINCI KCG 370G</t>
-  </si>
-  <si>
-    <t>10003422</t>
-  </si>
-  <si>
-    <t>GARUDA KC.GARING 350</t>
-  </si>
-  <si>
-    <t>10026500</t>
-  </si>
-  <si>
-    <t>DK KCNG BWNG PTH 180</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20040528</t>
-  </si>
-  <si>
-    <t>TIC TAC MIX 80G</t>
-  </si>
-  <si>
-    <t>20132864</t>
-  </si>
-  <si>
-    <t>TIC TAC MIE GORENG80</t>
-  </si>
-  <si>
-    <t>20023148</t>
-  </si>
-  <si>
-    <t>TIC TAC SAPI PNGG 80</t>
-  </si>
-  <si>
-    <t>20127483</t>
-  </si>
-  <si>
-    <t>GRUDA PILUS RDNG 80</t>
-  </si>
-  <si>
-    <t>20092875</t>
-  </si>
-  <si>
-    <t>GRUDA PILUS MI GR 80</t>
-  </si>
-  <si>
     <t>10026501</t>
   </si>
   <si>
@@ -1390,24 +1393,24 @@
     <t>GARUDA KCG.TELUR 110</t>
   </si>
   <si>
+    <t>20042632</t>
+  </si>
+  <si>
+    <t>IDM KCG ATOM PDS 140</t>
+  </si>
+  <si>
+    <t>20136516</t>
+  </si>
+  <si>
+    <t>IDM KC ATM CB IJO120</t>
+  </si>
+  <si>
     <t>20072370</t>
   </si>
   <si>
     <t>IDM KCNG BUMBU 150G</t>
   </si>
   <si>
-    <t>20042632</t>
-  </si>
-  <si>
-    <t>IDM KCG ATOM PDS 140</t>
-  </si>
-  <si>
-    <t>20136516</t>
-  </si>
-  <si>
-    <t>IDM KC ATM CB IJO120</t>
-  </si>
-  <si>
     <t>20072316</t>
   </si>
   <si>
@@ -1453,55 +1456,55 @@
     <t>GRUDA K.ATOM PDS 220</t>
   </si>
   <si>
+    <t>20137700</t>
+  </si>
+  <si>
+    <t>MAYASI CSHW KTCY 35G</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20066374</t>
+  </si>
+  <si>
+    <t>IDM MIX NUTS 80G</t>
+  </si>
+  <si>
+    <t>20104000</t>
+  </si>
+  <si>
+    <t>IDM KACANG ALMOND 65</t>
+  </si>
+  <si>
+    <t>20139150</t>
+  </si>
+  <si>
+    <t>IDM KCNG KORO BLD 80</t>
+  </si>
+  <si>
+    <t>10003507</t>
+  </si>
+  <si>
+    <t>MR.P KACANG MADU 80G</t>
+  </si>
+  <si>
+    <t>20047037</t>
+  </si>
+  <si>
+    <t>IDM KACANG BALI 150G</t>
+  </si>
+  <si>
     <t>20056977</t>
   </si>
   <si>
     <t>GARUDA ROSTA BWG 95</t>
   </si>
   <si>
-    <t>37</t>
-  </si>
-  <si>
     <t>20095753</t>
   </si>
   <si>
     <t>GRUDA ROSTA WGYU 95</t>
-  </si>
-  <si>
-    <t>20137700</t>
-  </si>
-  <si>
-    <t>MAYASI CSHW KTCY 35G</t>
-  </si>
-  <si>
-    <t>20066374</t>
-  </si>
-  <si>
-    <t>IDM MIX NUTS 80G</t>
-  </si>
-  <si>
-    <t>20104000</t>
-  </si>
-  <si>
-    <t>IDM KACANG ALMOND 65</t>
-  </si>
-  <si>
-    <t>20139150</t>
-  </si>
-  <si>
-    <t>IDM KCNG KORO BLD 80</t>
-  </si>
-  <si>
-    <t>10003507</t>
-  </si>
-  <si>
-    <t>MR.P KACANG MADU 80G</t>
-  </si>
-  <si>
-    <t>20047037</t>
-  </si>
-  <si>
-    <t>IDM KACANG BALI 150G</t>
   </si>
   <si>
     <t>20052766</t>
@@ -1951,7 +1954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F234"/>
+  <dimension ref="A1:F235"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2018,15 +2021,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -2035,10 +2038,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2058,7 +2061,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2092,21 +2095,21 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -2115,18 +2118,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -2135,18 +2138,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -2155,7 +2158,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -2163,10 +2166,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -2175,10 +2178,10 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2195,50 +2198,50 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2252,13 +2255,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2272,61 +2275,61 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -2338,15 +2341,15 @@
         <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -2358,15 +2361,15 @@
         <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -2375,18 +2378,18 @@
         <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -2398,15 +2401,15 @@
         <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -2415,350 +2418,350 @@
         <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2772,13 +2775,13 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2792,13 +2795,13 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2812,33 +2815,33 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>103</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2852,13 +2855,13 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2872,13 +2875,13 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2892,13 +2895,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2912,13 +2915,13 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2932,13 +2935,13 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2952,33 +2955,33 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2992,10 +2995,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>19</v>
@@ -3012,10 +3015,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>19</v>
@@ -3032,13 +3035,13 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3052,13 +3055,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3072,13 +3075,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3092,13 +3095,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3112,13 +3115,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3132,33 +3135,33 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>37</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3172,13 +3175,13 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>137</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3192,13 +3195,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3212,13 +3215,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3232,53 +3235,53 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>150</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -3292,13 +3295,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>150</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3312,10 +3315,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>19</v>
@@ -3332,13 +3335,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3352,13 +3355,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3372,13 +3375,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3392,13 +3395,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3412,13 +3415,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3432,33 +3435,33 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3472,13 +3475,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3492,10 +3495,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>19</v>
@@ -3512,13 +3515,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3532,33 +3535,33 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3572,13 +3575,13 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3592,13 +3595,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3612,10 +3615,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3632,33 +3635,33 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3672,13 +3675,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3692,13 +3695,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3712,13 +3715,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3732,13 +3735,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3752,33 +3755,33 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3792,13 +3795,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3812,13 +3815,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3832,13 +3835,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3858,7 +3861,7 @@
         <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3878,7 +3881,7 @@
         <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3895,10 +3898,10 @@
         <v>213</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3918,7 +3921,7 @@
         <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3935,10 +3938,10 @@
         <v>213</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3955,10 +3958,10 @@
         <v>213</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3978,7 +3981,7 @@
         <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3998,7 +4001,7 @@
         <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -4015,10 +4018,10 @@
         <v>226</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -4038,7 +4041,7 @@
         <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4055,10 +4058,10 @@
         <v>226</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4072,33 +4075,33 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4112,13 +4115,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4132,13 +4135,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4152,13 +4155,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4172,10 +4175,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -4192,33 +4195,33 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4232,13 +4235,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -4252,13 +4255,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4272,10 +4275,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
@@ -4292,33 +4295,33 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4332,13 +4335,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4352,13 +4355,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4372,13 +4375,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4392,153 +4395,153 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>37</v>
+        <v>272</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>274</v>
+        <v>42</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="E124" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>278</v>
+        <v>42</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>274</v>
+        <v>42</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4552,93 +4555,93 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="C134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="E134" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4652,13 +4655,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>37</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4672,53 +4675,53 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4732,13 +4735,13 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4752,73 +4755,73 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4832,13 +4835,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4852,73 +4855,73 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4932,13 +4935,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4952,93 +4955,93 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5052,13 +5055,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5072,30 +5075,30 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>19</v>
@@ -5103,62 +5106,62 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="E160" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5172,13 +5175,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5192,93 +5195,93 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="E166" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5292,130 +5295,130 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>19</v>
@@ -5423,19 +5426,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>19</v>
@@ -5443,19 +5446,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>19</v>
@@ -5463,1182 +5466,1202 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="E193" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="E200" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>449</v>
-      </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="E205" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>460</v>
-      </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>464</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="E212" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>473</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>475</v>
-      </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>477</v>
-      </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>482</v>
-      </c>
       <c r="E219" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B220" s="1" t="s">
-        <v>486</v>
-      </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>490</v>
-      </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D227" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D227" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="E227" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>503</v>
-      </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>507</v>
-      </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B234" s="1" t="s">
+      <c r="C234" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C234" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="E234" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F234" s="1" t="s">
-        <v>37</v>
+      <c r="B235" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F235" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="505">
   <si>
     <t/>
   </si>
@@ -19,7 +19,7 @@
     <t>20097776</t>
   </si>
   <si>
-    <t>JAPOTA HNY BUTTER 68</t>
+    <t>JAPOTA HNY BUTTER 65</t>
   </si>
   <si>
     <t>SNK06D</t>
@@ -34,7 +34,7 @@
     <t>20136745</t>
   </si>
   <si>
-    <t>JAPOTA PTATO ORI 68G</t>
+    <t>JAPOTA PTATO ORI 65G</t>
   </si>
   <si>
     <t>2</t>
@@ -46,7 +46,7 @@
     <t>20132250</t>
   </si>
   <si>
-    <t>JAPOTA BEEF BBQ 68G</t>
+    <t>JAPOTA BEEF BBQ 65G</t>
   </si>
   <si>
     <t>3</t>
@@ -55,7 +55,7 @@
     <t>20125580</t>
   </si>
   <si>
-    <t>JAPOTA NPS PDS 68G</t>
+    <t>JAPOTA NPS PDS 65G</t>
   </si>
   <si>
     <t>4</t>
@@ -76,7 +76,7 @@
     <t>20097774</t>
   </si>
   <si>
-    <t>JAPOTA JPN.SEAWD 68G</t>
+    <t>JAPOTA JPN.SEAWD 65G</t>
   </si>
   <si>
     <t>20131098</t>
@@ -274,87 +274,75 @@
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20139544</t>
-  </si>
-  <si>
-    <t>LAYS STAX SOUR&amp;O 70G</t>
+    <t>20023846</t>
+  </si>
+  <si>
+    <t>PRNGLES ORIGNAL 102G</t>
+  </si>
+  <si>
+    <t>20023845</t>
+  </si>
+  <si>
+    <t>PRINGLES CHEESY 102G</t>
+  </si>
+  <si>
+    <t>20044093</t>
+  </si>
+  <si>
+    <t>PRNGLES S.CRM&amp;O 102G</t>
+  </si>
+  <si>
+    <t>20141457</t>
+  </si>
+  <si>
+    <t>PRLGS BR SWD 102</t>
+  </si>
+  <si>
+    <t>RT,(E-27H)</t>
+  </si>
+  <si>
+    <t>20136007</t>
+  </si>
+  <si>
+    <t>MR.POTATO BBQ 85G</t>
+  </si>
+  <si>
+    <t>20135539</t>
+  </si>
+  <si>
+    <t>MR.POTATO ORGINAL85G</t>
+  </si>
+  <si>
+    <t>20135538</t>
+  </si>
+  <si>
+    <t>MR.POTATO SOUR&amp;O 85G</t>
+  </si>
+  <si>
+    <t>20137054</t>
+  </si>
+  <si>
+    <t>CHTATO LITE ASLI 110</t>
+  </si>
+  <si>
+    <t>20137572</t>
+  </si>
+  <si>
+    <t>CHTATO LITE KEJU 110</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>20139536</t>
-  </si>
-  <si>
-    <t>LAYS STAX ORGNL 70G</t>
+    <t>10000739</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PANG.35</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>20023846</t>
-  </si>
-  <si>
-    <t>PRNGLES ORIGNAL 102G</t>
-  </si>
-  <si>
-    <t>20023845</t>
-  </si>
-  <si>
-    <t>PRINGLES CHEESY 102G</t>
-  </si>
-  <si>
-    <t>20044093</t>
-  </si>
-  <si>
-    <t>PRNGLES S.CRM&amp;O 102G</t>
-  </si>
-  <si>
-    <t>20141457</t>
-  </si>
-  <si>
-    <t>PRLGS BR SWD 102</t>
-  </si>
-  <si>
-    <t>RT,(E-27H)</t>
-  </si>
-  <si>
-    <t>20136007</t>
-  </si>
-  <si>
-    <t>MR.POTATO BBQ 85G</t>
-  </si>
-  <si>
-    <t>20135539</t>
-  </si>
-  <si>
-    <t>MR.POTATO ORGINAL85G</t>
-  </si>
-  <si>
-    <t>20135538</t>
-  </si>
-  <si>
-    <t>MR.POTATO SOUR&amp;O 85G</t>
-  </si>
-  <si>
-    <t>20137054</t>
-  </si>
-  <si>
-    <t>CHTATO LITE ASLI 110</t>
-  </si>
-  <si>
-    <t>20137572</t>
-  </si>
-  <si>
-    <t>CHTATO LITE KEJU 110</t>
-  </si>
-  <si>
-    <t>10000739</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PANG.35</t>
-  </si>
-  <si>
     <t>20092063</t>
   </si>
   <si>
@@ -448,7 +436,7 @@
     <t>20115362</t>
   </si>
   <si>
-    <t>CHUBA KRP BALADO 125</t>
+    <t>CHUBA KRP BALADO 120</t>
   </si>
   <si>
     <t>RT,(E-1.5B)</t>
@@ -457,13 +445,13 @@
     <t>20115363</t>
   </si>
   <si>
-    <t>CHUBA KRPK BBQ 125G</t>
+    <t>CHUBA KRPK BBQ 120G</t>
   </si>
   <si>
     <t>20137973</t>
   </si>
   <si>
-    <t>CHUBA KRIPIK KEJU125</t>
+    <t>CHUBA KRIPIK KEJU120</t>
   </si>
   <si>
     <t>20093110</t>
@@ -583,24 +571,12 @@
     <t>14</t>
   </si>
   <si>
-    <t>20131518</t>
-  </si>
-  <si>
-    <t>KSUKA KRP KR.AYM 100</t>
-  </si>
-  <si>
     <t>20078113</t>
   </si>
   <si>
     <t>POPPY POP JGG BKR 60</t>
   </si>
   <si>
-    <t>20049993</t>
-  </si>
-  <si>
-    <t>SUKY2 SNCK UDG MNS60</t>
-  </si>
-  <si>
     <t>20034684</t>
   </si>
   <si>
@@ -1063,12 +1039,6 @@
     <t>M/SK NORI S.EGG2X4.5</t>
   </si>
   <si>
-    <t>20118737</t>
-  </si>
-  <si>
-    <t>M/SK NORI J.BKR2X4.5</t>
-  </si>
-  <si>
     <t>20138203</t>
   </si>
   <si>
@@ -1288,21 +1258,15 @@
     <t>MI GEMEZ SPICY 3X26G</t>
   </si>
   <si>
-    <t>20127483</t>
-  </si>
-  <si>
-    <t>GRUDA PILUS RDNG 80</t>
+    <t>20092875</t>
+  </si>
+  <si>
+    <t>GRUDA PILUS MI GR 80</t>
   </si>
   <si>
     <t>33</t>
   </si>
   <si>
-    <t>20092875</t>
-  </si>
-  <si>
-    <t>GRUDA PILUS MI GR 80</t>
-  </si>
-  <si>
     <t>20040528</t>
   </si>
   <si>
@@ -1408,7 +1372,7 @@
     <t>20072370</t>
   </si>
   <si>
-    <t>IDM KCNG BUMBU 150G</t>
+    <t>IDM KCNG BUMBU 100G</t>
   </si>
   <si>
     <t>20072316</t>
@@ -1954,7 +1918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F235"/>
+  <dimension ref="A1:F229"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2715,10 +2679,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>42</v>
@@ -2726,19 +2690,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>42</v>
@@ -2746,10 +2710,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2758,7 +2722,7 @@
         <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>42</v>
@@ -2766,10 +2730,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2778,18 +2742,18 @@
         <v>18</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2798,7 +2762,7 @@
         <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>42</v>
@@ -2806,10 +2770,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2818,18 +2782,18 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2838,7 +2802,7 @@
         <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>42</v>
@@ -2846,10 +2810,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2858,18 +2822,18 @@
         <v>18</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2878,18 +2842,18 @@
         <v>18</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2898,7 +2862,7 @@
         <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>9</v>
@@ -2918,7 +2882,7 @@
         <v>18</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>9</v>
@@ -2926,42 +2890,42 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2978,7 +2942,7 @@
         <v>85</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>19</v>
@@ -2998,10 +2962,10 @@
         <v>85</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3018,10 +2982,10 @@
         <v>85</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3038,7 +3002,7 @@
         <v>85</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>9</v>
@@ -3055,13 +3019,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3075,13 +3039,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3095,53 +3059,53 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>135</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3155,13 +3119,13 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>135</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3175,10 +3139,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>9</v>
@@ -3195,53 +3159,53 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>9</v>
+        <v>142</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>146</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3255,13 +3219,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>146</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3275,13 +3239,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -3295,13 +3259,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3315,13 +3279,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3335,10 +3299,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>9</v>
@@ -3355,10 +3319,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>9</v>
@@ -3375,13 +3339,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3395,10 +3359,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>9</v>
@@ -3406,42 +3370,42 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="E73" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3455,13 +3419,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3475,13 +3439,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3495,50 +3459,50 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>9</v>
@@ -3555,13 +3519,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3575,13 +3539,13 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3595,50 +3559,50 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>42</v>
@@ -3655,13 +3619,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3675,10 +3639,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>42</v>
@@ -3686,19 +3650,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>42</v>
@@ -3706,39 +3670,39 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>42</v>
@@ -3746,19 +3710,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>42</v>
@@ -3775,93 +3739,93 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>135</v>
+        <v>42</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3875,10 +3839,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>42</v>
@@ -3895,50 +3859,50 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>42</v>
@@ -3946,19 +3910,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>42</v>
@@ -3966,22 +3930,22 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3995,50 +3959,50 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>42</v>
@@ -4046,42 +4010,42 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4095,13 +4059,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4115,70 +4079,70 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -4186,22 +4150,22 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4215,10 +4179,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>9</v>
@@ -4226,19 +4190,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>9</v>
@@ -4246,62 +4210,62 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4315,70 +4279,70 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>42</v>
@@ -4386,39 +4350,39 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>272</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>42</v>
@@ -4435,10 +4399,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>42</v>
@@ -4455,10 +4419,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>42</v>
@@ -4466,39 +4430,39 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="E126" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>42</v>
@@ -4506,39 +4470,39 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>42</v>
@@ -4555,10 +4519,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>42</v>
@@ -4566,59 +4530,59 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>42</v>
+        <v>264</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>42</v>
@@ -4626,16 +4590,16 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>4</v>
@@ -4646,36 +4610,36 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>272</v>
+        <v>42</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>12</v>
@@ -4686,16 +4650,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>15</v>
@@ -4706,19 +4670,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>42</v>
@@ -4735,10 +4699,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>42</v>
@@ -4746,19 +4710,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>42</v>
@@ -4766,62 +4730,62 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4835,10 +4799,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>42</v>
@@ -4846,79 +4810,79 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="E145" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>42</v>
@@ -4935,10 +4899,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>42</v>
@@ -4955,93 +4919,93 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5055,110 +5019,110 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>42</v>
@@ -5175,113 +5139,113 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="E162" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5295,90 +5259,90 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="E168" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>19</v>
@@ -5386,119 +5350,119 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>42</v>
@@ -5515,10 +5479,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>42</v>
@@ -5535,10 +5499,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>42</v>
@@ -5555,10 +5519,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>42</v>
@@ -5575,10 +5539,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>42</v>
@@ -5586,19 +5550,19 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="E182" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>42</v>
@@ -5606,79 +5570,79 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>42</v>
@@ -5695,10 +5659,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>42</v>
@@ -5715,70 +5679,70 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="E189" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>42</v>
@@ -5786,19 +5750,19 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>42</v>
@@ -5806,19 +5770,19 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>42</v>
@@ -5835,10 +5799,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>42</v>
@@ -5846,19 +5810,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="E195" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>42</v>
@@ -5866,19 +5830,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>42</v>
@@ -5886,19 +5850,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>42</v>
@@ -5906,39 +5870,39 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>42</v>
@@ -5946,19 +5910,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B200" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="E200" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>42</v>
@@ -5966,19 +5930,19 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>42</v>
@@ -5986,19 +5950,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>42</v>
@@ -6006,19 +5970,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>42</v>
@@ -6026,39 +5990,39 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>42</v>
@@ -6075,10 +6039,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>42</v>
@@ -6086,19 +6050,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="E207" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>42</v>
@@ -6106,19 +6070,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>42</v>
@@ -6126,19 +6090,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>42</v>
@@ -6146,19 +6110,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>42</v>
@@ -6166,19 +6130,19 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>42</v>
@@ -6186,19 +6150,19 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>42</v>
@@ -6215,10 +6179,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>42</v>
@@ -6226,119 +6190,119 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D214" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D214" s="1" t="s">
-        <v>468</v>
-      </c>
       <c r="E214" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>42</v>
@@ -6355,13 +6319,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6375,10 +6339,10 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>86</v>
@@ -6386,19 +6350,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="E222" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>86</v>
@@ -6406,39 +6370,39 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>86</v>
@@ -6446,19 +6410,19 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>42</v>
@@ -6466,19 +6430,19 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>42</v>
@@ -6486,22 +6450,22 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6515,13 +6479,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6535,132 +6499,12 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A230" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="C230" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="E230" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F230" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A231" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="E231" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F231" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A232" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="E232" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F232" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A233" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D233" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="E233" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F233" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A234" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="E234" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F234" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="E235" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F235" s="1" t="s">
         <v>42</v>
       </c>
     </row>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="509">
   <si>
     <t/>
   </si>
@@ -697,7 +697,7 @@
     <t>20072195</t>
   </si>
   <si>
-    <t>MH MAITOS JG.BBQ 140</t>
+    <t>MH MAITOS JG.BBQ 120</t>
   </si>
   <si>
     <t>18</t>
@@ -706,7 +706,7 @@
     <t>20072194</t>
   </si>
   <si>
-    <t>MH MAITOS S.BLDO 140</t>
+    <t>MH MAITOS S.BLDO 120</t>
   </si>
   <si>
     <t>20099956</t>
@@ -1471,13 +1471,25 @@
     <t>GRUDA ROSTA WGYU 95</t>
   </si>
   <si>
+    <t>20054034</t>
+  </si>
+  <si>
+    <t>TAO K/N B/ROL CLS3.6</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>20056331</t>
+  </si>
+  <si>
+    <t>TAO KAE/N BR SPCY3.6</t>
+  </si>
+  <si>
     <t>20052766</t>
   </si>
   <si>
     <t>IDM KCNG METE MDU 80</t>
-  </si>
-  <si>
-    <t>38</t>
   </si>
   <si>
     <t>20096682</t>
@@ -1918,7 +1930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F229"/>
+  <dimension ref="A1:F231"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6345,7 +6357,7 @@
         <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6365,7 +6377,7 @@
         <v>8</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6425,7 +6437,7 @@
         <v>30</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6445,7 +6457,7 @@
         <v>33</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6505,6 +6517,46 @@
         <v>106</v>
       </c>
       <c r="F229" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F231" s="1" t="s">
         <v>42</v>
       </c>
     </row>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -469,13 +469,13 @@
     <t>20021029</t>
   </si>
   <si>
-    <t>QTELA KRPK BLDO 175G</t>
+    <t>QTELA KRPK BLD 175 G</t>
   </si>
   <si>
     <t>20012681</t>
   </si>
   <si>
-    <t>QTELA KRIPIK BBQ 175</t>
+    <t>QTELA KRPK BBQ 175 G</t>
   </si>
   <si>
     <t>20128427</t>
@@ -499,7 +499,7 @@
     <t>20012680</t>
   </si>
   <si>
-    <t>QTELA KRPK ORG 175G</t>
+    <t>QTELA KRPK ORG 175 G</t>
   </si>
   <si>
     <t>12</t>
@@ -526,7 +526,7 @@
     <t>20119437</t>
   </si>
   <si>
-    <t>POTABEE BBG 115G</t>
+    <t>POTABEE BBG 115 G</t>
   </si>
   <si>
     <t>20116675</t>
@@ -547,19 +547,19 @@
     <t>20134456</t>
   </si>
   <si>
-    <t>JAPOTA SEAWEED 115G</t>
+    <t>JAP POCH UMJPS 115 G</t>
   </si>
   <si>
     <t>20138949</t>
   </si>
   <si>
-    <t>JAPOTA H.HNY BTR 115</t>
+    <t>JAP POCH HPHOB 115 G</t>
   </si>
   <si>
     <t>20119460</t>
   </si>
   <si>
-    <t>POTABEE SEAWEED 115G</t>
+    <t>POTABEE SEA.W 115 G</t>
   </si>
   <si>
     <t>20137778</t>
@@ -1513,31 +1513,31 @@
     <t>20098348</t>
   </si>
   <si>
-    <t>REBO KUACI ORIGNL120</t>
+    <t>REBO KUACI ORI 120 G</t>
   </si>
   <si>
     <t>20068536</t>
   </si>
   <si>
-    <t>REBO KUACI G.TEA 120</t>
+    <t>REBO KUACI G.T 120 G</t>
   </si>
   <si>
     <t>20093909</t>
   </si>
   <si>
-    <t>REBO KUACI MILK 120</t>
+    <t>REBO KUACI MLK 120 G</t>
   </si>
   <si>
     <t>20098334</t>
   </si>
   <si>
-    <t>REBO KUACI CRM 120G</t>
+    <t>REBO KUACI CRM 120 G</t>
   </si>
   <si>
     <t>20130147</t>
   </si>
   <si>
-    <t>REBO KUACI CCNUT 120</t>
+    <t>REBO KUACI CNT 120 G</t>
   </si>
 </sst>
 </file>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="513">
   <si>
     <t/>
   </si>
@@ -274,6 +274,15 @@
     <t>PT,(E-1B)</t>
   </si>
   <si>
+    <t>20142905</t>
+  </si>
+  <si>
+    <t>PRNGLS SEAWD BRST 42</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>20023846</t>
   </si>
   <si>
@@ -349,9 +358,6 @@
     <t>CHITATO SAPI PGG 115</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>20002987</t>
   </si>
   <si>
@@ -388,6 +394,15 @@
     <t>QTELA TEMPE CABE/R55</t>
   </si>
   <si>
+    <t>20142837</t>
+  </si>
+  <si>
+    <t>QTLA UBI MIX JG.BK45</t>
+  </si>
+  <si>
+    <t>RT,(E-15H)</t>
+  </si>
+  <si>
     <t>20137014</t>
   </si>
   <si>
@@ -469,13 +484,13 @@
     <t>20021029</t>
   </si>
   <si>
-    <t>QTELA KRPK BLD 175 G</t>
+    <t>QTELA KRPK BLDO 175G</t>
   </si>
   <si>
     <t>20012681</t>
   </si>
   <si>
-    <t>QTELA KRPK BBQ 175 G</t>
+    <t>QTELA KRIPIK BBQ 175</t>
   </si>
   <si>
     <t>20128427</t>
@@ -499,7 +514,7 @@
     <t>20012680</t>
   </si>
   <si>
-    <t>QTELA KRPK ORG 175 G</t>
+    <t>QTELA KRPK ORG 175G</t>
   </si>
   <si>
     <t>12</t>
@@ -526,7 +541,7 @@
     <t>20119437</t>
   </si>
   <si>
-    <t>POTABEE BBG 115 G</t>
+    <t>POTABEE BBG 115G</t>
   </si>
   <si>
     <t>20116675</t>
@@ -547,19 +562,19 @@
     <t>20134456</t>
   </si>
   <si>
-    <t>JAP POCH UMJPS 115 G</t>
+    <t>JAPOTA SEAWEED 115G</t>
   </si>
   <si>
     <t>20138949</t>
   </si>
   <si>
-    <t>JAP POCH HPHOB 115 G</t>
+    <t>JAPOTA H.HNY BTR 115</t>
   </si>
   <si>
     <t>20119460</t>
   </si>
   <si>
-    <t>POTABEE SEA.W 115 G</t>
+    <t>POTABEE SEAWEED 115G</t>
   </si>
   <si>
     <t>20137778</t>
@@ -805,9 +820,6 @@
     <t>CHIKI NUTTY CRML 50G</t>
   </si>
   <si>
-    <t>RT,(E-15H)</t>
-  </si>
-  <si>
     <t>20142265</t>
   </si>
   <si>
@@ -1474,7 +1486,7 @@
     <t>20054034</t>
   </si>
   <si>
-    <t>TAO K/N B/ROL CLS3.6</t>
+    <t>TAO K/N B/ROL CLS 3G</t>
   </si>
   <si>
     <t>38</t>
@@ -1483,7 +1495,7 @@
     <t>20056331</t>
   </si>
   <si>
-    <t>TAO KAE/N BR SPCY3.6</t>
+    <t>TAO KAE/N BR SPCY 3G</t>
   </si>
   <si>
     <t>20052766</t>
@@ -1513,31 +1525,31 @@
     <t>20098348</t>
   </si>
   <si>
-    <t>REBO KUACI ORI 120 G</t>
+    <t>REBO KUACI ORIGNL120</t>
   </si>
   <si>
     <t>20068536</t>
   </si>
   <si>
-    <t>REBO KUACI G.T 120 G</t>
+    <t>REBO KUACI G.TEA 120</t>
   </si>
   <si>
     <t>20093909</t>
   </si>
   <si>
-    <t>REBO KUACI MLK 120 G</t>
+    <t>REBO KUACI MILK 120</t>
   </si>
   <si>
     <t>20098334</t>
   </si>
   <si>
-    <t>REBO KUACI CRM 120 G</t>
+    <t>REBO KUACI CRM 120G</t>
   </si>
   <si>
     <t>20130147</t>
   </si>
   <si>
-    <t>REBO KUACI CNT 120 G</t>
+    <t>REBO KUACI CCNUT 120</t>
   </si>
 </sst>
 </file>
@@ -1930,7 +1942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F231"/>
+  <dimension ref="A1:F233"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2691,10 +2703,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>42</v>
@@ -2702,10 +2714,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2714,7 +2726,7 @@
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>42</v>
@@ -2722,10 +2734,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2734,7 +2746,7 @@
         <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>42</v>
@@ -2742,10 +2754,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2754,10 +2766,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2774,18 +2786,18 @@
         <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2794,7 +2806,7 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>42</v>
@@ -2802,10 +2814,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2814,7 +2826,7 @@
         <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>42</v>
@@ -2822,10 +2834,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2834,18 +2846,18 @@
         <v>18</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2854,7 +2866,7 @@
         <v>18</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>9</v>
@@ -2911,13 +2923,13 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2934,7 +2946,7 @@
         <v>85</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>19</v>
@@ -2954,7 +2966,7 @@
         <v>85</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>19</v>
@@ -2974,10 +2986,10 @@
         <v>85</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2994,7 +3006,7 @@
         <v>85</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>9</v>
@@ -3014,7 +3026,7 @@
         <v>85</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>9</v>
@@ -3031,13 +3043,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3051,33 +3063,33 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>131</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3091,13 +3103,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>131</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3111,50 +3123,50 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>9</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>9</v>
@@ -3162,10 +3174,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -3174,10 +3186,10 @@
         <v>109</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>142</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3194,10 +3206,10 @@
         <v>109</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>142</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3211,61 +3223,61 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>42</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -3274,18 +3286,18 @@
         <v>112</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -3294,27 +3306,27 @@
         <v>112</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>9</v>
@@ -3322,19 +3334,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>9</v>
@@ -3342,39 +3354,39 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>163</v>
+        <v>89</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>9</v>
@@ -3391,13 +3403,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>163</v>
+        <v>89</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3411,73 +3423,73 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="E75" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3491,13 +3503,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3511,10 +3523,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>9</v>
@@ -3522,62 +3534,62 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3591,13 +3603,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3611,10 +3623,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>42</v>
@@ -3622,19 +3634,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>42</v>
@@ -3642,19 +3654,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>42</v>
@@ -3671,10 +3683,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>42</v>
@@ -3691,30 +3703,30 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>131</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>42</v>
@@ -3722,42 +3734,42 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3771,10 +3783,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>42</v>
@@ -3791,90 +3803,90 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>42</v>
@@ -3891,10 +3903,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>42</v>
@@ -3911,10 +3923,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>42</v>
@@ -3922,19 +3934,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>42</v>
@@ -3942,42 +3954,42 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>131</v>
+        <v>42</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3991,13 +4003,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>131</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -4011,93 +4023,93 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4111,13 +4123,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4131,10 +4143,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>9</v>
@@ -4142,62 +4154,62 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4211,13 +4223,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -4231,10 +4243,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>9</v>
@@ -4242,19 +4254,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>9</v>
@@ -4262,42 +4274,42 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4311,10 +4323,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>42</v>
@@ -4322,39 +4334,39 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>42</v>
@@ -4371,13 +4383,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4391,10 +4403,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>42</v>
@@ -4411,13 +4423,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4431,10 +4443,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>42</v>
@@ -4442,19 +4454,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>42</v>
@@ -4462,19 +4474,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>42</v>
@@ -4491,13 +4503,13 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4511,10 +4523,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>42</v>
@@ -4531,50 +4543,50 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>264</v>
+        <v>42</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>42</v>
@@ -4591,13 +4603,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4611,10 +4623,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>42</v>
@@ -4622,19 +4634,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>42</v>
@@ -4642,19 +4654,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>42</v>
@@ -4671,10 +4683,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>42</v>
@@ -4691,10 +4703,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>42</v>
@@ -4711,10 +4723,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>42</v>
@@ -4722,19 +4734,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>42</v>
@@ -4742,22 +4754,22 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4771,13 +4783,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4791,13 +4803,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4811,53 +4823,53 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4871,13 +4883,13 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4891,13 +4903,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4911,13 +4923,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4931,50 +4943,50 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>19</v>
@@ -4991,10 +5003,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>19</v>
@@ -5011,13 +5023,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5031,30 +5043,30 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>42</v>
@@ -5062,22 +5074,22 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="E157" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5091,13 +5103,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5111,13 +5123,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5131,13 +5143,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5151,50 +5163,50 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>9</v>
@@ -5211,10 +5223,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>9</v>
@@ -5231,10 +5243,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>9</v>
@@ -5251,13 +5263,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5271,30 +5283,30 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>19</v>
@@ -5302,22 +5314,22 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="E169" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5331,10 +5343,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>19</v>
@@ -5351,10 +5363,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>19</v>
@@ -5371,50 +5383,50 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="E174" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>42</v>
@@ -5431,10 +5443,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>42</v>
@@ -5451,10 +5463,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>42</v>
@@ -5471,10 +5483,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>42</v>
@@ -5491,10 +5503,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>42</v>
@@ -5511,10 +5523,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>42</v>
@@ -5531,10 +5543,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>42</v>
@@ -5551,10 +5563,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>42</v>
@@ -5562,19 +5574,19 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>42</v>
@@ -5582,22 +5594,22 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="E183" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -5611,13 +5623,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5631,13 +5643,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5651,13 +5663,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5671,13 +5683,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5691,10 +5703,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>42</v>
@@ -5702,19 +5714,19 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>42</v>
@@ -5722,19 +5734,19 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="C190" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="E190" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>42</v>
@@ -5751,10 +5763,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>42</v>
@@ -5771,10 +5783,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>42</v>
@@ -5791,10 +5803,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>42</v>
@@ -5811,10 +5823,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>42</v>
@@ -5822,19 +5834,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>42</v>
@@ -5842,19 +5854,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="C196" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="E196" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>42</v>
@@ -5871,10 +5883,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>42</v>
@@ -5891,13 +5903,13 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5911,10 +5923,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>42</v>
@@ -5922,39 +5934,39 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B201" s="1" t="s">
+      <c r="C201" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="C201" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="E201" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>42</v>
@@ -5971,10 +5983,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>42</v>
@@ -5991,10 +6003,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>42</v>
@@ -6011,10 +6023,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>42</v>
@@ -6031,10 +6043,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>42</v>
@@ -6051,10 +6063,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>42</v>
@@ -6062,19 +6074,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>42</v>
@@ -6082,19 +6094,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>42</v>
@@ -6111,10 +6123,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>42</v>
@@ -6131,10 +6143,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>42</v>
@@ -6151,10 +6163,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>42</v>
@@ -6171,10 +6183,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>42</v>
@@ -6191,10 +6203,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>42</v>
@@ -6202,42 +6214,42 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>473</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="E215" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6251,10 +6263,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>86</v>
@@ -6271,13 +6283,13 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -6291,10 +6303,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>86</v>
@@ -6311,13 +6323,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6331,13 +6343,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6351,53 +6363,53 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>490</v>
-      </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B223" s="1" t="s">
+      <c r="C223" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D223" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="C223" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="E223" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6411,13 +6423,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6431,10 +6443,10 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>86</v>
@@ -6451,10 +6463,10 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>86</v>
@@ -6471,13 +6483,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6491,13 +6503,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6511,10 +6523,10 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>42</v>
@@ -6531,10 +6543,10 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>42</v>
@@ -6551,12 +6563,52 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E231" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E232" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F231" s="1" t="s">
+      <c r="F232" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F233" s="1" t="s">
         <v>42</v>
       </c>
     </row>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -238,6 +238,12 @@
     <t>PRINGLES SOURS CRM42</t>
   </si>
   <si>
+    <t>20142905</t>
+  </si>
+  <si>
+    <t>PRNGLS SEAWD BRST 42</t>
+  </si>
+  <si>
     <t>20129961</t>
   </si>
   <si>
@@ -262,102 +268,96 @@
     <t>MR PTT BULDAK CHES40</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>20139841</t>
   </si>
   <si>
     <t>MR POTATO CRBNARA 40</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20142905</t>
-  </si>
-  <si>
-    <t>PRNGLS SEAWD BRST 42</t>
+    <t>20023846</t>
+  </si>
+  <si>
+    <t>PRNGLES ORIGNAL 102G</t>
+  </si>
+  <si>
+    <t>20023845</t>
+  </si>
+  <si>
+    <t>PRINGLES CHEESY 102G</t>
+  </si>
+  <si>
+    <t>20044093</t>
+  </si>
+  <si>
+    <t>PRNGLES S.CRM&amp;O 102G</t>
+  </si>
+  <si>
+    <t>20141457</t>
+  </si>
+  <si>
+    <t>PRLGS BR SWD 102</t>
+  </si>
+  <si>
+    <t>RT,(E-27H)</t>
+  </si>
+  <si>
+    <t>20136007</t>
+  </si>
+  <si>
+    <t>MR.POTATO BBQ 85G</t>
+  </si>
+  <si>
+    <t>20135539</t>
+  </si>
+  <si>
+    <t>MR.POTATO ORGINAL85G</t>
+  </si>
+  <si>
+    <t>20135538</t>
+  </si>
+  <si>
+    <t>MR.POTATO SOUR&amp;O 85G</t>
+  </si>
+  <si>
+    <t>20137054</t>
+  </si>
+  <si>
+    <t>CHTATO LITE ASLI 110</t>
+  </si>
+  <si>
+    <t>20137572</t>
+  </si>
+  <si>
+    <t>CHTATO LITE KEJU 110</t>
+  </si>
+  <si>
+    <t>10000739</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PANG.35</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20092063</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PGG 115</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>20023846</t>
-  </si>
-  <si>
-    <t>PRNGLES ORIGNAL 102G</t>
-  </si>
-  <si>
-    <t>20023845</t>
-  </si>
-  <si>
-    <t>PRINGLES CHEESY 102G</t>
-  </si>
-  <si>
-    <t>20044093</t>
-  </si>
-  <si>
-    <t>PRNGLES S.CRM&amp;O 102G</t>
-  </si>
-  <si>
-    <t>20141457</t>
-  </si>
-  <si>
-    <t>PRLGS BR SWD 102</t>
-  </si>
-  <si>
-    <t>RT,(E-27H)</t>
-  </si>
-  <si>
-    <t>20136007</t>
-  </si>
-  <si>
-    <t>MR.POTATO BBQ 85G</t>
-  </si>
-  <si>
-    <t>20135539</t>
-  </si>
-  <si>
-    <t>MR.POTATO ORGINAL85G</t>
-  </si>
-  <si>
-    <t>20135538</t>
-  </si>
-  <si>
-    <t>MR.POTATO SOUR&amp;O 85G</t>
-  </si>
-  <si>
-    <t>20137054</t>
-  </si>
-  <si>
-    <t>CHTATO LITE ASLI 110</t>
-  </si>
-  <si>
-    <t>20137572</t>
-  </si>
-  <si>
-    <t>CHTATO LITE KEJU 110</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10000739</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PANG.35</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20092063</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 115</t>
-  </si>
-  <si>
     <t>20002987</t>
   </si>
   <si>
@@ -703,84 +703,84 @@
     <t>PANCHOS CABE PDS 145</t>
   </si>
   <si>
+    <t>20098166</t>
+  </si>
+  <si>
+    <t>HAPPYTOS JG.BKR 140</t>
+  </si>
+  <si>
+    <t>20072195</t>
+  </si>
+  <si>
+    <t>MH MAITOS JG.BBQ 120</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20072194</t>
+  </si>
+  <si>
+    <t>MH MAITOS S.BLDO 120</t>
+  </si>
+  <si>
+    <t>20099956</t>
+  </si>
+  <si>
+    <t>PANCHOS PEDAS 140G</t>
+  </si>
+  <si>
+    <t>20099955</t>
+  </si>
+  <si>
+    <t>PANCHOS SAPI.PG 140G</t>
+  </si>
+  <si>
+    <t>10036957</t>
+  </si>
+  <si>
+    <t>HAPPYTOS CHIP HJU140</t>
+  </si>
+  <si>
+    <t>20070033</t>
+  </si>
+  <si>
+    <t>HAPPYTOS NC.CHS 140G</t>
+  </si>
+  <si>
+    <t>20116112</t>
+  </si>
+  <si>
+    <t>MAXICORN BBQ 130G</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20116110</t>
+  </si>
+  <si>
+    <t>MXCORN ROAST.CR 130G</t>
+  </si>
+  <si>
+    <t>20116125</t>
+  </si>
+  <si>
+    <t>MXCORN NCHO CHS 130G</t>
+  </si>
+  <si>
+    <t>10002101</t>
+  </si>
+  <si>
+    <t>HAPPYTOS CHIP MRH140</t>
+  </si>
+  <si>
     <t>20119019</t>
   </si>
   <si>
     <t>HAPPYTOS HOT CHL 140</t>
   </si>
   <si>
-    <t>20072195</t>
-  </si>
-  <si>
-    <t>MH MAITOS JG.BBQ 120</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20072194</t>
-  </si>
-  <si>
-    <t>MH MAITOS S.BLDO 120</t>
-  </si>
-  <si>
-    <t>20099956</t>
-  </si>
-  <si>
-    <t>PANCHOS PEDAS 140G</t>
-  </si>
-  <si>
-    <t>20099955</t>
-  </si>
-  <si>
-    <t>PANCHOS SAPI.PG 140G</t>
-  </si>
-  <si>
-    <t>20098166</t>
-  </si>
-  <si>
-    <t>HAPPYTOS JG.BKR 140</t>
-  </si>
-  <si>
-    <t>20070033</t>
-  </si>
-  <si>
-    <t>HAPPYTOS NC.CHS 140G</t>
-  </si>
-  <si>
-    <t>20116112</t>
-  </si>
-  <si>
-    <t>MAXICORN BBQ 130G</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20116110</t>
-  </si>
-  <si>
-    <t>MXCORN ROAST.CR 130G</t>
-  </si>
-  <si>
-    <t>20116125</t>
-  </si>
-  <si>
-    <t>MXCORN NCHO CHS 130G</t>
-  </si>
-  <si>
-    <t>10002101</t>
-  </si>
-  <si>
-    <t>HAPPYTOS CHIP MRH140</t>
-  </si>
-  <si>
-    <t>10036957</t>
-  </si>
-  <si>
-    <t>HAPPYTOS CHIP HJU140</t>
-  </si>
-  <si>
     <t>20104942</t>
   </si>
   <si>
@@ -814,12 +814,6 @@
     <t>CHIKI P/C SALT CRM72</t>
   </si>
   <si>
-    <t>20140264</t>
-  </si>
-  <si>
-    <t>CHIKI NUTTY CRML 50G</t>
-  </si>
-  <si>
     <t>20142265</t>
   </si>
   <si>
@@ -901,6 +895,12 @@
     <t>23</t>
   </si>
   <si>
+    <t>20143053</t>
+  </si>
+  <si>
+    <t>CETOS SWTS KJ MNS120</t>
+  </si>
+  <si>
     <t>20140272</t>
   </si>
   <si>
@@ -1369,18 +1369,18 @@
     <t>GARUDA KCG.TELUR 110</t>
   </si>
   <si>
+    <t>20136516</t>
+  </si>
+  <si>
+    <t>IDM KC ATM CB IJO120</t>
+  </si>
+  <si>
     <t>20042632</t>
   </si>
   <si>
     <t>IDM KCG ATOM PDS 140</t>
   </si>
   <si>
-    <t>20136516</t>
-  </si>
-  <si>
-    <t>IDM KC ATM CB IJO120</t>
-  </si>
-  <si>
     <t>20072370</t>
   </si>
   <si>
@@ -1441,6 +1441,18 @@
     <t>37</t>
   </si>
   <si>
+    <t>20052766</t>
+  </si>
+  <si>
+    <t>IDM KCNG METE MDU 80</t>
+  </si>
+  <si>
+    <t>20096682</t>
+  </si>
+  <si>
+    <t>IDM KACANG JUMBO 80</t>
+  </si>
+  <si>
     <t>20066374</t>
   </si>
   <si>
@@ -1496,18 +1508,6 @@
   </si>
   <si>
     <t>TAO KAE/N BR SPCY 3G</t>
-  </si>
-  <si>
-    <t>20052766</t>
-  </si>
-  <si>
-    <t>IDM KCNG METE MDU 80</t>
-  </si>
-  <si>
-    <t>20096682</t>
-  </si>
-  <si>
-    <t>IDM KACANG JUMBO 80</t>
   </si>
   <si>
     <t>20112944</t>
@@ -2689,15 +2689,15 @@
         <v>85</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2706,10 +2706,10 @@
         <v>33</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2886,7 +2886,7 @@
         <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>9</v>
@@ -2894,10 +2894,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2906,7 +2906,7 @@
         <v>18</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>9</v>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2926,7 +2926,7 @@
         <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>9</v>
@@ -3083,7 +3083,7 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>4</v>
@@ -3103,7 +3103,7 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>8</v>
@@ -3123,7 +3123,7 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>12</v>
@@ -3143,7 +3143,7 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>15</v>
@@ -3163,7 +3163,7 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>30</v>
@@ -3183,7 +3183,7 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>33</v>
@@ -3203,7 +3203,7 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>18</v>
@@ -3223,7 +3223,7 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>4</v>
@@ -3243,7 +3243,7 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>8</v>
@@ -3263,7 +3263,7 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>12</v>
@@ -3283,7 +3283,7 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>15</v>
@@ -3303,7 +3303,7 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>30</v>
@@ -3323,7 +3323,7 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>4</v>
@@ -3343,7 +3343,7 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>8</v>
@@ -3363,7 +3363,7 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>12</v>
@@ -3383,7 +3383,7 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>15</v>
@@ -3403,7 +3403,7 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>30</v>
@@ -3646,7 +3646,7 @@
         <v>190</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>42</v>
@@ -3666,7 +3666,7 @@
         <v>190</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>42</v>
@@ -3686,7 +3686,7 @@
         <v>190</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>42</v>
@@ -4343,30 +4343,30 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>42</v>
@@ -4383,10 +4383,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>42</v>
@@ -4403,13 +4403,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4423,13 +4423,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4443,10 +4443,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>42</v>
@@ -4463,10 +4463,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>42</v>
@@ -4474,19 +4474,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>42</v>
@@ -4503,10 +4503,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>42</v>
@@ -4523,13 +4523,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4543,13 +4543,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4563,10 +4563,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>42</v>
@@ -4574,19 +4574,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>42</v>
@@ -4603,10 +4603,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>129</v>
@@ -4623,10 +4623,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>42</v>
@@ -4643,10 +4643,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>42</v>
@@ -4909,7 +4909,7 @@
         <v>12</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4929,7 +4929,7 @@
         <v>15</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -5066,7 +5066,7 @@
         <v>339</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>42</v>
@@ -5586,7 +5586,7 @@
         <v>387</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>42</v>
@@ -5746,7 +5746,7 @@
         <v>421</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>42</v>
@@ -5766,7 +5766,7 @@
         <v>421</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>42</v>
@@ -5786,7 +5786,7 @@
         <v>421</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>42</v>
@@ -5806,7 +5806,7 @@
         <v>421</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>42</v>
@@ -5826,7 +5826,7 @@
         <v>421</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>42</v>
@@ -5846,7 +5846,7 @@
         <v>421</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>42</v>
@@ -5949,7 +5949,7 @@
         <v>30</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6269,7 +6269,7 @@
         <v>8</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6289,7 +6289,7 @@
         <v>12</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -6309,7 +6309,7 @@
         <v>15</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6329,7 +6329,7 @@
         <v>30</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6349,7 +6349,7 @@
         <v>33</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6369,7 +6369,7 @@
         <v>18</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6389,7 +6389,7 @@
         <v>85</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6403,53 +6403,53 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B225" s="1" t="s">
+      <c r="C225" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D225" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="C225" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D225" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="E225" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6463,13 +6463,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6483,13 +6483,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6503,13 +6503,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6523,10 +6523,10 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>42</v>
@@ -6543,10 +6543,10 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>42</v>
@@ -6563,10 +6563,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>42</v>
@@ -6583,10 +6583,10 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>42</v>
@@ -6603,10 +6603,10 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>42</v>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="517">
   <si>
     <t/>
   </si>
@@ -358,6 +358,12 @@
     <t>11</t>
   </si>
   <si>
+    <t>20137778</t>
+  </si>
+  <si>
+    <t>CHIMI JG.BKR 85G</t>
+  </si>
+  <si>
     <t>20002987</t>
   </si>
   <si>
@@ -376,216 +382,222 @@
     <t>KUSUKA RMPT LAUT 60</t>
   </si>
   <si>
+    <t>20012678</t>
+  </si>
+  <si>
+    <t>QTELA KERIPIK ORG 60</t>
+  </si>
+  <si>
+    <t>20012679</t>
+  </si>
+  <si>
+    <t>QTELA KRIPIK BBQ 60</t>
+  </si>
+  <si>
+    <t>20021032</t>
+  </si>
+  <si>
+    <t>QTELA KERIPIK BLD 60</t>
+  </si>
+  <si>
+    <t>20093110</t>
+  </si>
+  <si>
+    <t>KUSUKA BALADO 180G</t>
+  </si>
+  <si>
+    <t>20137014</t>
+  </si>
+  <si>
+    <t>CHIMI KRP CHS.BR 41G</t>
+  </si>
+  <si>
+    <t>20131047</t>
+  </si>
+  <si>
+    <t>CHIMI KR.MENTEGA 41</t>
+  </si>
+  <si>
+    <t>20104728</t>
+  </si>
+  <si>
+    <t>CHIMI KRP.UB JG.BK41</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20104729</t>
+  </si>
+  <si>
+    <t>CHIMI KRP.UB JG.BL41</t>
+  </si>
+  <si>
+    <t>20142837</t>
+  </si>
+  <si>
+    <t>QTLA UBI MIX JG.BK45</t>
+  </si>
+  <si>
+    <t>RT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20143260</t>
+  </si>
+  <si>
+    <t>KUSUKA UBI MADU 42G</t>
+  </si>
+  <si>
+    <t>20115362</t>
+  </si>
+  <si>
+    <t>CHUBA KRP BALADO 120</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20115363</t>
+  </si>
+  <si>
+    <t>CHUBA KRPK BBQ 120G</t>
+  </si>
+  <si>
+    <t>20137973</t>
+  </si>
+  <si>
+    <t>CHUBA KRIPIK KEJU120</t>
+  </si>
+  <si>
+    <t>20000516</t>
+  </si>
+  <si>
+    <t>KUSUKA KRPK BBQ 180</t>
+  </si>
+  <si>
+    <t>20093109</t>
+  </si>
+  <si>
+    <t>KUSUKA ORIGINAL 180G</t>
+  </si>
+  <si>
+    <t>20012680</t>
+  </si>
+  <si>
+    <t>QTELA KRPK ORG 175G</t>
+  </si>
+  <si>
+    <t>20021029</t>
+  </si>
+  <si>
+    <t>QTELA KRPK BLDO 175G</t>
+  </si>
+  <si>
+    <t>20012681</t>
+  </si>
+  <si>
+    <t>QTELA KRIPIK BBQ 175</t>
+  </si>
+  <si>
+    <t>20128427</t>
+  </si>
+  <si>
+    <t>QTELA KS RP.LAUT 100</t>
+  </si>
+  <si>
+    <t>20124903</t>
+  </si>
+  <si>
+    <t>QTELA KR AY LD/HT100</t>
+  </si>
+  <si>
+    <t>20140882</t>
+  </si>
+  <si>
+    <t>LAYS WAVY SAPI 105G</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20122571</t>
+  </si>
+  <si>
+    <t>PIATTOS SAPI PG 115G</t>
+  </si>
+  <si>
+    <t>20143172</t>
+  </si>
+  <si>
+    <t>PIATTOS RM.LAUT 115</t>
+  </si>
+  <si>
+    <t>20134572</t>
+  </si>
+  <si>
+    <t>PIATTOS SMB GPRK 115</t>
+  </si>
+  <si>
+    <t>20119437</t>
+  </si>
+  <si>
+    <t>POTABEE BBG 115G</t>
+  </si>
+  <si>
+    <t>20116675</t>
+  </si>
+  <si>
+    <t>CHTATO LITE NORI 115</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20139538</t>
+  </si>
+  <si>
+    <t>LAYS RMPT LAUT 105G</t>
+  </si>
+  <si>
+    <t>20134456</t>
+  </si>
+  <si>
+    <t>JAPOTA SEAWEED 115G</t>
+  </si>
+  <si>
+    <t>20138949</t>
+  </si>
+  <si>
+    <t>JAPOTA H.HNY BTR 115</t>
+  </si>
+  <si>
+    <t>20119460</t>
+  </si>
+  <si>
+    <t>POTABEE SEAWEED 115G</t>
+  </si>
+  <si>
     <t>20056958</t>
   </si>
   <si>
     <t>QTELA TEMPE R/LAUT55</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20045104</t>
+  </si>
+  <si>
+    <t>QTELA TEMPE CABE/R55</t>
+  </si>
+  <si>
     <t>20033450</t>
   </si>
   <si>
     <t>QTELA KRP/TMPE ORI55</t>
   </si>
   <si>
-    <t>20045104</t>
-  </si>
-  <si>
-    <t>QTELA TEMPE CABE/R55</t>
-  </si>
-  <si>
-    <t>20142837</t>
-  </si>
-  <si>
-    <t>QTLA UBI MIX JG.BK45</t>
-  </si>
-  <si>
-    <t>RT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20137014</t>
-  </si>
-  <si>
-    <t>CHIMI KRP CHS.BR 41G</t>
-  </si>
-  <si>
-    <t>20131047</t>
-  </si>
-  <si>
-    <t>CHIMI KR.MENTEGA 41</t>
-  </si>
-  <si>
-    <t>20104728</t>
-  </si>
-  <si>
-    <t>CHIMI KRP.UB JG.BK41</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20104729</t>
-  </si>
-  <si>
-    <t>CHIMI KRP.UB JG.BL41</t>
-  </si>
-  <si>
-    <t>20021032</t>
-  </si>
-  <si>
-    <t>QTELA KERIPIK BLD 60</t>
-  </si>
-  <si>
-    <t>20012678</t>
-  </si>
-  <si>
-    <t>QTELA KERIPIK ORG 60</t>
-  </si>
-  <si>
-    <t>20012679</t>
-  </si>
-  <si>
-    <t>QTELA KRIPIK BBQ 60</t>
-  </si>
-  <si>
-    <t>20115362</t>
-  </si>
-  <si>
-    <t>CHUBA KRP BALADO 120</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20115363</t>
-  </si>
-  <si>
-    <t>CHUBA KRPK BBQ 120G</t>
-  </si>
-  <si>
-    <t>20137973</t>
-  </si>
-  <si>
-    <t>CHUBA KRIPIK KEJU120</t>
-  </si>
-  <si>
-    <t>20093110</t>
-  </si>
-  <si>
-    <t>KUSUKA BALADO 180G</t>
-  </si>
-  <si>
-    <t>20000516</t>
-  </si>
-  <si>
-    <t>KUSUKA KRPK BBQ 180</t>
-  </si>
-  <si>
-    <t>20021029</t>
-  </si>
-  <si>
-    <t>QTELA KRPK BLDO 175G</t>
-  </si>
-  <si>
-    <t>20012681</t>
-  </si>
-  <si>
-    <t>QTELA KRIPIK BBQ 175</t>
-  </si>
-  <si>
-    <t>20128427</t>
-  </si>
-  <si>
-    <t>QTELA KS RP.LAUT 100</t>
-  </si>
-  <si>
-    <t>20124903</t>
-  </si>
-  <si>
-    <t>QTELA KR AY LD/HT100</t>
-  </si>
-  <si>
-    <t>20093109</t>
-  </si>
-  <si>
-    <t>KUSUKA ORIGINAL 180G</t>
-  </si>
-  <si>
-    <t>20012680</t>
-  </si>
-  <si>
-    <t>QTELA KRPK ORG 175G</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20140882</t>
-  </si>
-  <si>
-    <t>LAYS WAVY SAPI 105G</t>
-  </si>
-  <si>
-    <t>20122571</t>
-  </si>
-  <si>
-    <t>PIATTOS SAPI PG 115G</t>
-  </si>
-  <si>
-    <t>20134572</t>
-  </si>
-  <si>
-    <t>PIATTOS SMB GPRK 115</t>
-  </si>
-  <si>
-    <t>20119437</t>
-  </si>
-  <si>
-    <t>POTABEE BBG 115G</t>
-  </si>
-  <si>
-    <t>20116675</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 115</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20139538</t>
-  </si>
-  <si>
-    <t>LAYS RMPT LAUT 105G</t>
-  </si>
-  <si>
-    <t>20134456</t>
-  </si>
-  <si>
-    <t>JAPOTA SEAWEED 115G</t>
-  </si>
-  <si>
-    <t>20138949</t>
-  </si>
-  <si>
-    <t>JAPOTA H.HNY BTR 115</t>
-  </si>
-  <si>
-    <t>20119460</t>
-  </si>
-  <si>
-    <t>POTABEE SEAWEED 115G</t>
-  </si>
-  <si>
-    <t>20137778</t>
-  </si>
-  <si>
-    <t>CHIMI JG.BKR 85G</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>20078113</t>
   </si>
   <si>
@@ -985,15 +997,21 @@
     <t>CHIKI BALL CHOC 200G</t>
   </si>
   <si>
+    <t>20097391</t>
+  </si>
+  <si>
+    <t>M/SK NORI S.EGG2X4.5</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
     <t>20117923</t>
   </si>
   <si>
     <t>T K NOI S/LVR ORI2'S</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>20117928</t>
   </si>
   <si>
@@ -1045,18 +1063,24 @@
     <t>M/SUKA NORI PDS2X4.5</t>
   </si>
   <si>
-    <t>20097391</t>
-  </si>
-  <si>
-    <t>M/SK NORI S.EGG2X4.5</t>
-  </si>
-  <si>
     <t>20138203</t>
   </si>
   <si>
     <t>M/SK GIM BORI BIG 3G</t>
   </si>
   <si>
+    <t>20054034</t>
+  </si>
+  <si>
+    <t>TAO K/N B/ROL CLS 3G</t>
+  </si>
+  <si>
+    <t>20056331</t>
+  </si>
+  <si>
+    <t>TAO KAE/N BR SPCY 3G</t>
+  </si>
+  <si>
     <t>10006890</t>
   </si>
   <si>
@@ -1495,25 +1519,13 @@
     <t>GRUDA ROSTA WGYU 95</t>
   </si>
   <si>
-    <t>20054034</t>
-  </si>
-  <si>
-    <t>TAO K/N B/ROL CLS 3G</t>
+    <t>20112944</t>
+  </si>
+  <si>
+    <t>IDM KUACI SUSU 80G</t>
   </si>
   <si>
     <t>38</t>
-  </si>
-  <si>
-    <t>20056331</t>
-  </si>
-  <si>
-    <t>TAO KAE/N BR SPCY 3G</t>
-  </si>
-  <si>
-    <t>20112944</t>
-  </si>
-  <si>
-    <t>IDM KUACI SUSU 80G</t>
   </si>
   <si>
     <t>20093516</t>
@@ -1942,7 +1954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F233"/>
+  <dimension ref="A1:F235"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2949,7 +2961,7 @@
         <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3009,7 +3021,7 @@
         <v>15</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3069,15 +3081,15 @@
         <v>18</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -3089,15 +3101,15 @@
         <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -3114,10 +3126,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -3129,15 +3141,15 @@
         <v>12</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>136</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -3149,15 +3161,15 @@
         <v>15</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -3169,15 +3181,15 @@
         <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>9</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -3189,7 +3201,7 @@
         <v>33</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>9</v>
+        <v>142</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3209,7 +3221,7 @@
         <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3409,7 +3421,7 @@
         <v>30</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3429,7 +3441,7 @@
         <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3449,7 +3461,7 @@
         <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3469,7 +3481,7 @@
         <v>12</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3629,7 +3641,7 @@
         <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3649,7 +3661,7 @@
         <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3669,7 +3681,7 @@
         <v>12</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3703,10 +3715,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>42</v>
@@ -3714,19 +3726,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>42</v>
@@ -3734,22 +3746,22 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="C90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="E90" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>136</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3763,10 +3775,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>42</v>
@@ -3783,13 +3795,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3803,30 +3815,30 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>42</v>
@@ -3834,22 +3846,22 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3863,13 +3875,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3883,13 +3895,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3903,13 +3915,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3923,10 +3935,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>42</v>
@@ -3934,19 +3946,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>42</v>
@@ -3954,19 +3966,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>42</v>
@@ -3983,10 +3995,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>42</v>
@@ -4003,13 +4015,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -4023,53 +4035,53 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>136</v>
+        <v>42</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="C106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4083,13 +4095,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4103,13 +4115,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4123,13 +4135,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4143,50 +4155,50 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>9</v>
@@ -4203,13 +4215,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4223,13 +4235,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -4243,50 +4255,50 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>9</v>
@@ -4303,10 +4315,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>9</v>
@@ -4323,13 +4335,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4343,30 +4355,30 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>42</v>
@@ -4374,19 +4386,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>42</v>
@@ -4403,13 +4415,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4423,10 +4435,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>42</v>
@@ -4443,13 +4455,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4463,10 +4475,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>42</v>
@@ -4474,19 +4486,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>42</v>
@@ -4494,19 +4506,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>42</v>
@@ -4523,13 +4535,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4543,10 +4555,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>42</v>
@@ -4563,30 +4575,30 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>42</v>
@@ -4594,22 +4606,22 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4623,10 +4635,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>42</v>
@@ -4643,13 +4655,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>42</v>
+        <v>142</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4663,10 +4675,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>42</v>
@@ -4674,19 +4686,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>42</v>
@@ -4694,19 +4706,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>42</v>
@@ -4723,10 +4735,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>42</v>
@@ -4743,10 +4755,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>42</v>
@@ -4763,10 +4775,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>42</v>
@@ -4774,19 +4786,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>42</v>
@@ -4794,22 +4806,22 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4823,13 +4835,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4843,13 +4855,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4863,53 +4875,53 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>89</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4923,13 +4935,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4943,10 +4955,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>42</v>
@@ -4963,13 +4975,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4983,70 +4995,70 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>19</v>
@@ -5063,13 +5075,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5083,30 +5095,30 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>42</v>
@@ -5114,62 +5126,62 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="E161" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5183,10 +5195,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>42</v>
@@ -5203,90 +5215,90 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="E167" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>9</v>
@@ -5303,13 +5315,13 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5323,70 +5335,70 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>19</v>
@@ -5394,22 +5406,22 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5423,90 +5435,90 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>42</v>
@@ -5523,10 +5535,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>42</v>
@@ -5543,10 +5555,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>42</v>
@@ -5563,10 +5575,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>42</v>
@@ -5583,10 +5595,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>42</v>
@@ -5603,10 +5615,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>42</v>
@@ -5614,19 +5626,19 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>42</v>
@@ -5634,62 +5646,62 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="E187" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5703,10 +5715,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>42</v>
@@ -5723,13 +5735,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5743,50 +5755,50 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>42</v>
@@ -5794,19 +5806,19 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>42</v>
@@ -5814,19 +5826,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="E194" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>42</v>
@@ -5843,10 +5855,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>42</v>
@@ -5863,10 +5875,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>42</v>
@@ -5874,19 +5886,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>42</v>
@@ -5894,19 +5906,19 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>42</v>
@@ -5914,19 +5926,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>42</v>
@@ -5934,22 +5946,22 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="E200" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5963,10 +5975,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>42</v>
@@ -5974,19 +5986,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>42</v>
@@ -5994,19 +6006,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>449</v>
-      </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>42</v>
@@ -6014,39 +6026,39 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="E205" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>42</v>
@@ -6063,10 +6075,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>42</v>
@@ -6083,10 +6095,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>42</v>
@@ -6103,10 +6115,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>42</v>
@@ -6114,19 +6126,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>42</v>
@@ -6134,19 +6146,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>464</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>42</v>
@@ -6154,19 +6166,19 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>42</v>
@@ -6174,19 +6186,19 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>460</v>
-      </c>
       <c r="E212" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>42</v>
@@ -6203,10 +6215,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>42</v>
@@ -6223,10 +6235,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>42</v>
@@ -6243,10 +6255,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>42</v>
@@ -6254,82 +6266,82 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>477</v>
-      </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B219" s="1" t="s">
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="C219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>475</v>
-      </c>
       <c r="E219" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6343,10 +6355,10 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>89</v>
@@ -6363,13 +6375,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6383,10 +6395,10 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>89</v>
@@ -6403,13 +6415,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6423,13 +6435,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6443,10 +6455,10 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>19</v>
@@ -6454,82 +6466,82 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="B229" s="1" t="s">
+      <c r="C229" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D229" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="C229" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="E229" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6543,13 +6555,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6563,10 +6575,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>42</v>
@@ -6583,10 +6595,10 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>42</v>
@@ -6603,12 +6615,52 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="F233" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F235" s="1" t="s">
         <v>42</v>
       </c>
     </row>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="516">
   <si>
     <t/>
   </si>
@@ -880,12 +880,6 @@
     <t>TIC TIC STCK BWNG 70</t>
   </si>
   <si>
-    <t>20103371</t>
-  </si>
-  <si>
-    <t>TIC TIC STK BWG+SS65</t>
-  </si>
-  <si>
     <t>20072575</t>
   </si>
   <si>
@@ -1069,6 +1063,15 @@
     <t>M/SK GIM BORI BIG 3G</t>
   </si>
   <si>
+    <t>20143287</t>
+  </si>
+  <si>
+    <t>JYO KOR SWD ORI 4.8</t>
+  </si>
+  <si>
+    <t>,(E-27H)</t>
+  </si>
+  <si>
     <t>20054034</t>
   </si>
   <si>
@@ -1411,19 +1414,13 @@
     <t>IDM KCNG BUMBU 100G</t>
   </si>
   <si>
-    <t>20072316</t>
-  </si>
-  <si>
-    <t>D/K SUKRO KEDELE 95G</t>
+    <t>20062966</t>
+  </si>
+  <si>
+    <t>DK SUKRO BBQ 95G</t>
   </si>
   <si>
     <t>36</t>
-  </si>
-  <si>
-    <t>20062966</t>
-  </si>
-  <si>
-    <t>DK SUKRO BBQ 95G</t>
   </si>
   <si>
     <t>20084707</t>
@@ -1954,7 +1951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F235"/>
+  <dimension ref="A1:F234"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4558,10 +4555,10 @@
         <v>286</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4578,10 +4575,10 @@
         <v>286</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4595,10 +4592,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>42</v>
@@ -4606,19 +4603,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>42</v>
@@ -4635,13 +4632,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>42</v>
+        <v>142</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4655,13 +4652,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>142</v>
+        <v>42</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4675,10 +4672,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>42</v>
@@ -4695,10 +4692,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>42</v>
@@ -4706,19 +4703,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>42</v>
@@ -4735,10 +4732,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>42</v>
@@ -4755,10 +4752,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>42</v>
@@ -4775,10 +4772,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>42</v>
@@ -4795,10 +4792,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>42</v>
@@ -4806,19 +4803,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>42</v>
@@ -4835,13 +4832,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4855,10 +4852,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>19</v>
@@ -4875,13 +4872,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4895,33 +4892,33 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4935,10 +4932,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>42</v>
@@ -4955,13 +4952,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4975,10 +4972,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>89</v>
@@ -4995,13 +4992,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5015,10 +5012,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>42</v>
@@ -5035,30 +5032,30 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>19</v>
@@ -5075,10 +5072,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>19</v>
@@ -5095,13 +5092,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5115,27 +5112,27 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>42</v>
+        <v>352</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>33</v>
@@ -5146,16 +5143,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>18</v>
@@ -5166,16 +5163,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>4</v>
@@ -5186,16 +5183,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>358</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>8</v>
@@ -5206,16 +5203,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>12</v>
@@ -5226,16 +5223,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>15</v>
@@ -5246,16 +5243,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>30</v>
@@ -5266,16 +5263,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>33</v>
@@ -5286,16 +5283,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>4</v>
@@ -5306,16 +5303,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>8</v>
@@ -5326,16 +5323,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>12</v>
@@ -5346,16 +5343,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>15</v>
@@ -5366,16 +5363,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>30</v>
@@ -5386,16 +5383,16 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>33</v>
@@ -5406,16 +5403,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>4</v>
@@ -5426,16 +5423,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>8</v>
@@ -5446,16 +5443,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>12</v>
@@ -5466,16 +5463,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>15</v>
@@ -5486,16 +5483,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>30</v>
@@ -5506,16 +5503,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>4</v>
@@ -5526,16 +5523,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>395</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>8</v>
@@ -5546,16 +5543,16 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>12</v>
@@ -5566,16 +5563,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>15</v>
@@ -5586,16 +5583,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>30</v>
@@ -5606,16 +5603,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>33</v>
@@ -5626,16 +5623,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>18</v>
@@ -5646,16 +5643,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>85</v>
@@ -5666,16 +5663,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>88</v>
@@ -5686,16 +5683,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>4</v>
@@ -5706,16 +5703,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>8</v>
@@ -5726,16 +5723,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>12</v>
@@ -5746,16 +5743,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>15</v>
@@ -5766,16 +5763,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>30</v>
@@ -5786,16 +5783,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>33</v>
@@ -5806,16 +5803,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>18</v>
@@ -5826,16 +5823,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>4</v>
@@ -5846,16 +5843,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>429</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>8</v>
@@ -5866,16 +5863,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>12</v>
@@ -5886,16 +5883,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>15</v>
@@ -5906,16 +5903,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>30</v>
@@ -5926,16 +5923,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>33</v>
@@ -5946,16 +5943,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>4</v>
@@ -5966,16 +5963,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>442</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>8</v>
@@ -5986,16 +5983,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>12</v>
@@ -6006,16 +6003,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>15</v>
@@ -6026,16 +6023,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>30</v>
@@ -6046,16 +6043,16 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>4</v>
@@ -6066,16 +6063,16 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>453</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>8</v>
@@ -6086,16 +6083,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>12</v>
@@ -6106,16 +6103,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>15</v>
@@ -6126,16 +6123,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>30</v>
@@ -6146,16 +6143,16 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>33</v>
@@ -6166,16 +6163,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>18</v>
@@ -6186,19 +6183,19 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>42</v>
@@ -6206,19 +6203,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>468</v>
-      </c>
       <c r="E213" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>42</v>
@@ -6226,19 +6223,19 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>42</v>
@@ -6246,19 +6243,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>42</v>
@@ -6266,19 +6263,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>42</v>
@@ -6286,19 +6283,19 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>42</v>
@@ -6306,19 +6303,19 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>42</v>
@@ -6326,39 +6323,39 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B219" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="C219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="E219" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>89</v>
@@ -6366,19 +6363,19 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>89</v>
@@ -6386,19 +6383,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>89</v>
@@ -6406,19 +6403,19 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>89</v>
@@ -6426,79 +6423,79 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>89</v>
+        <v>19</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>42</v>
@@ -6506,39 +6503,39 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B229" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D229" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C229" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>504</v>
-      </c>
       <c r="E229" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>89</v>
@@ -6546,39 +6543,39 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>42</v>
@@ -6586,19 +6583,19 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>42</v>
@@ -6606,19 +6603,19 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>42</v>
@@ -6626,41 +6623,21 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E235" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F235" s="1" t="s">
         <v>42</v>
       </c>
     </row>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="515">
   <si>
     <t/>
   </si>
@@ -124,7 +124,7 @@
     <t>20116686</t>
   </si>
   <si>
-    <t>CHTATO LITE C/ONN 68</t>
+    <t>C/LITE SRCRM ONION65</t>
   </si>
   <si>
     <t>20131037</t>
@@ -163,7 +163,7 @@
     <t>20116684</t>
   </si>
   <si>
-    <t>CHTATO LITE SLMON 68</t>
+    <t>C/LITE SLMON TRYKI65</t>
   </si>
   <si>
     <t>20139713</t>
@@ -1067,9 +1067,6 @@
   </si>
   <si>
     <t>JYO KOR SWD ORI 4.8</t>
-  </si>
-  <si>
-    <t>,(E-27H)</t>
   </si>
   <si>
     <t>20054034</t>
@@ -5118,15 +5115,15 @@
         <v>30</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>352</v>
+        <v>98</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
@@ -5143,10 +5140,10 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
@@ -5163,16 +5160,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>4</v>
@@ -5183,16 +5180,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>8</v>
@@ -5203,16 +5200,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>12</v>
@@ -5223,16 +5220,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>15</v>
@@ -5243,16 +5240,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>30</v>
@@ -5263,16 +5260,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>33</v>
@@ -5283,16 +5280,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>4</v>
@@ -5303,16 +5300,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>8</v>
@@ -5323,16 +5320,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>12</v>
@@ -5343,16 +5340,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>15</v>
@@ -5363,16 +5360,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>30</v>
@@ -5383,16 +5380,16 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>33</v>
@@ -5403,16 +5400,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>4</v>
@@ -5423,16 +5420,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>8</v>
@@ -5443,16 +5440,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>12</v>
@@ -5463,16 +5460,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>15</v>
@@ -5483,16 +5480,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>30</v>
@@ -5503,16 +5500,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>4</v>
@@ -5523,16 +5520,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>8</v>
@@ -5543,16 +5540,16 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>12</v>
@@ -5563,16 +5560,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>15</v>
@@ -5583,16 +5580,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>30</v>
@@ -5603,16 +5600,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>33</v>
@@ -5623,16 +5620,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>18</v>
@@ -5643,16 +5640,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>85</v>
@@ -5663,16 +5660,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>88</v>
@@ -5683,16 +5680,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>415</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>4</v>
@@ -5703,16 +5700,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>8</v>
@@ -5723,16 +5720,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>12</v>
@@ -5743,16 +5740,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>15</v>
@@ -5763,16 +5760,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>30</v>
@@ -5783,16 +5780,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>33</v>
@@ -5803,16 +5800,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>18</v>
@@ -5823,16 +5820,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>430</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>4</v>
@@ -5843,16 +5840,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>8</v>
@@ -5863,16 +5860,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>12</v>
@@ -5883,16 +5880,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>15</v>
@@ -5903,16 +5900,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>30</v>
@@ -5923,16 +5920,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>33</v>
@@ -5943,16 +5940,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>443</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>4</v>
@@ -5963,16 +5960,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>8</v>
@@ -5983,16 +5980,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>12</v>
@@ -6003,16 +6000,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>449</v>
-      </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>15</v>
@@ -6023,16 +6020,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>30</v>
@@ -6043,16 +6040,16 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>4</v>
@@ -6063,16 +6060,16 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>8</v>
@@ -6083,16 +6080,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>12</v>
@@ -6103,16 +6100,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>460</v>
-      </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>15</v>
@@ -6123,16 +6120,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>30</v>
@@ -6143,16 +6140,16 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>464</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>33</v>
@@ -6163,16 +6160,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>18</v>
@@ -6183,16 +6180,16 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>8</v>
@@ -6203,16 +6200,16 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>12</v>
@@ -6223,16 +6220,16 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>473</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>15</v>
@@ -6243,16 +6240,16 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>475</v>
-      </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>30</v>
@@ -6263,16 +6260,16 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>477</v>
-      </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>33</v>
@@ -6283,16 +6280,16 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>18</v>
@@ -6303,16 +6300,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B218" s="1" t="s">
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>482</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>4</v>
@@ -6323,16 +6320,16 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>8</v>
@@ -6343,16 +6340,16 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B220" s="1" t="s">
-        <v>486</v>
-      </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>12</v>
@@ -6363,16 +6360,16 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>15</v>
@@ -6383,16 +6380,16 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>490</v>
-      </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>30</v>
@@ -6403,16 +6400,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>33</v>
@@ -6423,16 +6420,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>18</v>
@@ -6443,16 +6440,16 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>85</v>
@@ -6463,16 +6460,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>88</v>
@@ -6483,16 +6480,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>111</v>
@@ -6503,16 +6500,16 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="B228" s="1" t="s">
+      <c r="C228" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D228" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D228" s="1" t="s">
-        <v>503</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>4</v>
@@ -6523,16 +6520,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>8</v>
@@ -6543,16 +6540,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>507</v>
-      </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>12</v>
@@ -6563,16 +6560,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>15</v>
@@ -6583,16 +6580,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>30</v>
@@ -6603,16 +6600,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>33</v>
@@ -6623,16 +6620,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>18</v>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="522">
   <si>
     <t/>
   </si>
@@ -1159,15 +1159,21 @@
     <t>TARO SNACK BARBQ 32G</t>
   </si>
   <si>
+    <t>20143734</t>
+  </si>
+  <si>
+    <t>CHOCLTS PLW CHCO97.5</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>20097777</t>
   </si>
   <si>
     <t>KRISBEE PLW CHO 100G</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>20081238</t>
   </si>
   <si>
@@ -1294,13 +1300,28 @@
     <t>MI GEMEZ SPICY 3X26G</t>
   </si>
   <si>
+    <t>20143335</t>
+  </si>
+  <si>
+    <t>MI KRMZ SHR AY PGG4S</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
+    <t>10035883</t>
+  </si>
+  <si>
+    <t>GARUDA PILUS PDS 80G</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
     <t>20092875</t>
   </si>
   <si>
     <t>GRUDA PILUS MI GR 80</t>
-  </si>
-  <si>
-    <t>33</t>
   </si>
   <si>
     <t>20040528</t>
@@ -1948,7 +1969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F234"/>
+  <dimension ref="A1:F237"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -5415,7 +5436,7 @@
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5435,7 +5456,7 @@
         <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5509,30 +5530,30 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>42</v>
@@ -5549,10 +5570,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>42</v>
@@ -5569,10 +5590,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>42</v>
@@ -5589,10 +5610,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>42</v>
@@ -5609,10 +5630,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>42</v>
@@ -5629,10 +5650,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>42</v>
@@ -5649,10 +5670,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>42</v>
@@ -5669,10 +5690,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>42</v>
@@ -5689,10 +5710,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>42</v>
@@ -5700,19 +5721,19 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>42</v>
@@ -5729,13 +5750,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5749,13 +5770,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5769,10 +5790,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>9</v>
@@ -5789,13 +5810,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5809,10 +5830,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>42</v>
@@ -5829,10 +5850,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>42</v>
@@ -5840,22 +5861,22 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F195" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5869,10 +5890,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>42</v>
@@ -5880,19 +5901,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>429</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>42</v>
@@ -5900,19 +5921,19 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>42</v>
@@ -5920,19 +5941,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>42</v>
@@ -5940,19 +5961,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>42</v>
@@ -5969,10 +5990,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>42</v>
@@ -5989,10 +6010,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>42</v>
@@ -6009,10 +6030,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>42</v>
@@ -6020,39 +6041,39 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="E204" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>42</v>
@@ -6069,10 +6090,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>42</v>
@@ -6089,13 +6110,13 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6109,10 +6130,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>42</v>
@@ -6120,19 +6141,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D209" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="E209" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>42</v>
@@ -6140,19 +6161,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>42</v>
@@ -6160,19 +6181,19 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>42</v>
@@ -6180,19 +6201,19 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>42</v>
@@ -6209,10 +6230,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>42</v>
@@ -6229,10 +6250,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>42</v>
@@ -6249,10 +6270,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>42</v>
@@ -6260,19 +6281,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>468</v>
-      </c>
       <c r="E216" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>42</v>
@@ -6280,19 +6301,19 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>42</v>
@@ -6300,19 +6321,19 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>42</v>
@@ -6329,13 +6350,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6349,13 +6370,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6369,30 +6390,30 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="E222" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>89</v>
@@ -6400,19 +6421,19 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>89</v>
@@ -6420,39 +6441,39 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>89</v>
@@ -6460,59 +6481,59 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>89</v>
@@ -6529,13 +6550,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6549,10 +6570,10 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>42</v>
@@ -6569,50 +6590,50 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D232" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="E232" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>42</v>
@@ -6620,21 +6641,81 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="E234" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F235" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F236" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="E237" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F234" s="1" t="s">
+      <c r="F237" s="1" t="s">
         <v>42</v>
       </c>
     </row>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="521">
   <si>
     <t/>
   </si>
@@ -1177,7 +1177,7 @@
     <t>20081238</t>
   </si>
   <si>
-    <t>TARO NET TRYK BBQ 62</t>
+    <t>TARO NET TRYK BBQ 65</t>
   </si>
   <si>
     <t>20055205</t>
@@ -1306,9 +1306,6 @@
     <t>MI KRMZ SHR AY PGG4S</t>
   </si>
   <si>
-    <t>,(E-1B)</t>
-  </si>
-  <si>
     <t>10035883</t>
   </si>
   <si>
@@ -1405,13 +1402,13 @@
     <t>10029724</t>
   </si>
   <si>
-    <t>GARUDA KCNG ATOM 100</t>
+    <t>GARUDA KCNG ATOM 95</t>
   </si>
   <si>
     <t>10003840</t>
   </si>
   <si>
-    <t>GARUDA KCG.TELUR 110</t>
+    <t>GARUDA KCG.TELUR 100</t>
   </si>
   <si>
     <t>20136516</t>
@@ -1456,13 +1453,13 @@
     <t>20120796</t>
   </si>
   <si>
-    <t>GRUDA ROSTA JG.B 95</t>
+    <t>GRUDA ROSTA JG.B 90</t>
   </si>
   <si>
     <t>20089490</t>
   </si>
   <si>
-    <t>GARUDA ROSTA PDS 90G</t>
+    <t>GARUDA ROSTA PDS 85G</t>
   </si>
   <si>
     <t>10005355</t>
@@ -1525,13 +1522,13 @@
     <t>20056977</t>
   </si>
   <si>
-    <t>GARUDA ROSTA BWG 95</t>
+    <t>GARUDA ROSTA BWG 90</t>
   </si>
   <si>
     <t>20095753</t>
   </si>
   <si>
-    <t>GRUDA ROSTA WGYU 95</t>
+    <t>GRUDA ROSTA WGYU 90</t>
   </si>
   <si>
     <t>20112944</t>
@@ -5876,21 +5873,21 @@
         <v>85</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>431</v>
+        <v>42</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="C196" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>434</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>4</v>
@@ -5901,16 +5898,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>8</v>
@@ -5921,16 +5918,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>12</v>
@@ -5941,16 +5938,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>15</v>
@@ -5961,16 +5958,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>30</v>
@@ -5981,16 +5978,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>33</v>
@@ -6001,16 +5998,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>18</v>
@@ -6021,16 +6018,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>4</v>
@@ -6041,16 +6038,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>8</v>
@@ -6061,16 +6058,16 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>12</v>
@@ -6081,16 +6078,16 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>455</v>
-      </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>15</v>
@@ -6101,16 +6098,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>30</v>
@@ -6121,16 +6118,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>4</v>
@@ -6141,16 +6138,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>8</v>
@@ -6161,16 +6158,16 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>464</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>12</v>
@@ -6181,16 +6178,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>15</v>
@@ -6201,16 +6198,16 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>468</v>
-      </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>30</v>
@@ -6221,16 +6218,16 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>33</v>
@@ -6241,16 +6238,16 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>472</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>18</v>
@@ -6261,16 +6258,16 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>475</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>8</v>
@@ -6281,16 +6278,16 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>477</v>
-      </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>12</v>
@@ -6301,16 +6298,16 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>15</v>
@@ -6321,16 +6318,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>30</v>
@@ -6341,16 +6338,16 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>33</v>
@@ -6361,16 +6358,16 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B220" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>18</v>
@@ -6381,16 +6378,16 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="B221" s="1" t="s">
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>4</v>
@@ -6401,16 +6398,16 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>490</v>
-      </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>8</v>
@@ -6421,16 +6418,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>12</v>
@@ -6441,16 +6438,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>15</v>
@@ -6461,16 +6458,16 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>30</v>
@@ -6481,16 +6478,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>33</v>
@@ -6501,16 +6498,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>18</v>
@@ -6521,16 +6518,16 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>85</v>
@@ -6541,16 +6538,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>504</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>88</v>
@@ -6561,16 +6558,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>506</v>
-      </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>111</v>
@@ -6581,16 +6578,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B231" s="1" t="s">
+      <c r="C231" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D231" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>509</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>4</v>
@@ -6601,16 +6598,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>8</v>
@@ -6621,16 +6618,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>12</v>
@@ -6641,16 +6638,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>15</v>
@@ -6661,16 +6658,16 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>517</v>
-      </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>30</v>
@@ -6681,16 +6678,16 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>519</v>
-      </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>33</v>
@@ -6701,16 +6698,16 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>521</v>
-      </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>18</v>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="519">
   <si>
     <t/>
   </si>
@@ -61,207 +61,201 @@
     <t>4</t>
   </si>
   <si>
-    <t>20094328</t>
-  </si>
-  <si>
-    <t>PIATTOS SMB GPREK 65</t>
+    <t>20097774</t>
+  </si>
+  <si>
+    <t>JAPOTA JPN.SEAWD 65G</t>
+  </si>
+  <si>
+    <t>20131098</t>
+  </si>
+  <si>
+    <t>POTABEE SPICY BBQ 65</t>
+  </si>
+  <si>
+    <t>20093941</t>
+  </si>
+  <si>
+    <t>POTABEE AYM BKR 65G</t>
+  </si>
+  <si>
+    <t>20071780</t>
+  </si>
+  <si>
+    <t>POTABEE CHIP BBQ 65G</t>
+  </si>
+  <si>
+    <t>20071781</t>
+  </si>
+  <si>
+    <t>POTABEE CHIP SWD 65G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20025762</t>
+  </si>
+  <si>
+    <t>PIATTOS SAPI PNG 65G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20132750</t>
+  </si>
+  <si>
+    <t>CHITATO AYAM BWG 65G</t>
+  </si>
+  <si>
+    <t>20116686</t>
+  </si>
+  <si>
+    <t>C/LITE SRCRM ONION65</t>
+  </si>
+  <si>
+    <t>20131037</t>
+  </si>
+  <si>
+    <t>CHTATOLITE ABR.SWD65</t>
+  </si>
+  <si>
+    <t>20138228</t>
+  </si>
+  <si>
+    <t>LAYS RUMPUT LAUT 64G</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20138229</t>
+  </si>
+  <si>
+    <t>LAYS DGG SAPI BKR64G</t>
+  </si>
+  <si>
+    <t>20141504</t>
+  </si>
+  <si>
+    <t>LAYS RMPT LAUT PDS64</t>
+  </si>
+  <si>
+    <t>20116670</t>
+  </si>
+  <si>
+    <t>CHTATO LITE NORI 65G</t>
+  </si>
+  <si>
+    <t>20116684</t>
+  </si>
+  <si>
+    <t>C/LITE SLMON TRYKI65</t>
+  </si>
+  <si>
+    <t>20139713</t>
+  </si>
+  <si>
+    <t>CHITATO BEEF MALA 65</t>
+  </si>
+  <si>
+    <t>20136744</t>
+  </si>
+  <si>
+    <t>CHITATO TTEOK-BK 65G</t>
+  </si>
+  <si>
+    <t>20141944</t>
+  </si>
+  <si>
+    <t>CHITATO RNDG SAPI 62</t>
+  </si>
+  <si>
+    <t>10001094</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PGG 65G</t>
+  </si>
+  <si>
+    <t>20122264</t>
+  </si>
+  <si>
+    <t>CHITATO MI GORENG 65</t>
+  </si>
+  <si>
+    <t>10001093</t>
+  </si>
+  <si>
+    <t>CHITATO AYAM BMB 65G</t>
+  </si>
+  <si>
+    <t>20014506</t>
+  </si>
+  <si>
+    <t>CHITATO CHEESE SPR65</t>
+  </si>
+  <si>
+    <t>20023435</t>
+  </si>
+  <si>
+    <t>CHITATO SP BMB BKR65</t>
+  </si>
+  <si>
+    <t>20029228</t>
+  </si>
+  <si>
+    <t>CHITATO AYAM BBQ 65G</t>
+  </si>
+  <si>
+    <t>20052859</t>
+  </si>
+  <si>
+    <t>PRINGLES ORIGINAL 42</t>
+  </si>
+  <si>
+    <t>20111009</t>
+  </si>
+  <si>
+    <t>PRINGLES CHSY CHS 42</t>
+  </si>
+  <si>
+    <t>20052860</t>
+  </si>
+  <si>
+    <t>PRINGLES SOURS CRM42</t>
+  </si>
+  <si>
+    <t>20142905</t>
+  </si>
+  <si>
+    <t>PRNGLS SEAWD BRST 42</t>
+  </si>
+  <si>
+    <t>20129961</t>
+  </si>
+  <si>
+    <t>MR.POTATO ORG KLG 35</t>
+  </si>
+  <si>
+    <t>20106307</t>
+  </si>
+  <si>
+    <t>MR.POTATO GHOST/P 40</t>
+  </si>
+  <si>
+    <t>20120198</t>
+  </si>
+  <si>
+    <t>MR/P GHST/P SWEED40</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20097774</t>
-  </si>
-  <si>
-    <t>JAPOTA JPN.SEAWD 65G</t>
-  </si>
-  <si>
-    <t>20131098</t>
-  </si>
-  <si>
-    <t>POTABEE SPICY BBQ 65</t>
-  </si>
-  <si>
-    <t>20093941</t>
-  </si>
-  <si>
-    <t>POTABEE AYM BKR 65G</t>
-  </si>
-  <si>
-    <t>20071780</t>
-  </si>
-  <si>
-    <t>POTABEE CHIP BBQ 65G</t>
-  </si>
-  <si>
-    <t>20071781</t>
-  </si>
-  <si>
-    <t>POTABEE CHIP SWD 65G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20025762</t>
-  </si>
-  <si>
-    <t>PIATTOS SAPI PNG 65G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20132750</t>
-  </si>
-  <si>
-    <t>CHITATO AYAM BWG 65G</t>
-  </si>
-  <si>
-    <t>20116686</t>
-  </si>
-  <si>
-    <t>C/LITE SRCRM ONION65</t>
-  </si>
-  <si>
-    <t>20131037</t>
-  </si>
-  <si>
-    <t>CHTATOLITE ABR.SWD65</t>
-  </si>
-  <si>
-    <t>20138228</t>
-  </si>
-  <si>
-    <t>LAYS RUMPUT LAUT 64G</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138229</t>
-  </si>
-  <si>
-    <t>LAYS DGG SAPI BKR64G</t>
-  </si>
-  <si>
-    <t>20141504</t>
-  </si>
-  <si>
-    <t>LAYS RMPT LAUT PDS64</t>
-  </si>
-  <si>
-    <t>20116670</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 65G</t>
-  </si>
-  <si>
-    <t>20116684</t>
-  </si>
-  <si>
-    <t>C/LITE SLMON TRYKI65</t>
-  </si>
-  <si>
-    <t>20139713</t>
-  </si>
-  <si>
-    <t>CHITATO BEEF MALA 65</t>
-  </si>
-  <si>
-    <t>20136744</t>
-  </si>
-  <si>
-    <t>CHITATO TTEOK-BK 65G</t>
-  </si>
-  <si>
-    <t>20141944</t>
-  </si>
-  <si>
-    <t>CHITATO RNDG SAPI 62</t>
-  </si>
-  <si>
-    <t>10001094</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 65G</t>
-  </si>
-  <si>
-    <t>20122264</t>
-  </si>
-  <si>
-    <t>CHITATO MI GORENG 65</t>
-  </si>
-  <si>
-    <t>10001093</t>
-  </si>
-  <si>
-    <t>CHITATO AYAM BMB 65G</t>
-  </si>
-  <si>
-    <t>20014506</t>
-  </si>
-  <si>
-    <t>CHITATO CHEESE SPR65</t>
-  </si>
-  <si>
-    <t>20023435</t>
-  </si>
-  <si>
-    <t>CHITATO SP BMB BKR65</t>
-  </si>
-  <si>
-    <t>20029228</t>
-  </si>
-  <si>
-    <t>CHITATO AYAM BBQ 65G</t>
-  </si>
-  <si>
-    <t>20052859</t>
-  </si>
-  <si>
-    <t>PRINGLES ORIGINAL 42</t>
-  </si>
-  <si>
-    <t>20111009</t>
-  </si>
-  <si>
-    <t>PRINGLES CHSY CHS 42</t>
-  </si>
-  <si>
-    <t>20052860</t>
-  </si>
-  <si>
-    <t>PRINGLES SOURS CRM42</t>
-  </si>
-  <si>
-    <t>20142905</t>
-  </si>
-  <si>
-    <t>PRNGLS SEAWD BRST 42</t>
-  </si>
-  <si>
-    <t>20129961</t>
-  </si>
-  <si>
-    <t>MR.POTATO ORG KLG 35</t>
-  </si>
-  <si>
-    <t>20106307</t>
-  </si>
-  <si>
-    <t>MR.POTATO GHOST/P 40</t>
-  </si>
-  <si>
-    <t>20120198</t>
-  </si>
-  <si>
-    <t>MR/P GHST/P SWEED40</t>
-  </si>
-  <si>
     <t>20141098</t>
   </si>
   <si>
@@ -286,25 +280,25 @@
     <t>20023846</t>
   </si>
   <si>
-    <t>PRNGLES ORIGNAL 102G</t>
+    <t>PRNGLES ORI 102 G</t>
   </si>
   <si>
     <t>20023845</t>
   </si>
   <si>
-    <t>PRINGLES CHEESY 102G</t>
+    <t>PRINGLES CHESY 102 G</t>
   </si>
   <si>
     <t>20044093</t>
   </si>
   <si>
-    <t>PRNGLES S.CRM&amp;O 102G</t>
+    <t>PRNGLES S.C&amp;O 102 G</t>
   </si>
   <si>
     <t>20141457</t>
   </si>
   <si>
-    <t>PRLGS BR SWD 102</t>
+    <t>PRNGLES BR SWD 102 G</t>
   </si>
   <si>
     <t>RT,(E-27H)</t>
@@ -634,13 +628,13 @@
     <t>20139291</t>
   </si>
   <si>
-    <t>FLOATY SNACK BWNG 60</t>
+    <t>FLOATY BAWANG 60 G</t>
   </si>
   <si>
     <t>20140056</t>
   </si>
   <si>
-    <t>FLOATY TERSERAH 60G</t>
+    <t>FLOATY TERSERAH 60 G</t>
   </si>
   <si>
     <t>20141100</t>
@@ -1123,7 +1117,7 @@
     <t>20114756</t>
   </si>
   <si>
-    <t>GURIBEE BBQ BLDO 65G</t>
+    <t>GURIBEE BBQ BLDO 62G</t>
   </si>
   <si>
     <t>29</t>
@@ -1132,13 +1126,13 @@
     <t>20114757</t>
   </si>
   <si>
-    <t>GURIBEE RMP.LAUT 65G</t>
+    <t>GURIBEE RMP.LAUT 62G</t>
   </si>
   <si>
     <t>20130511</t>
   </si>
   <si>
-    <t>GURIBEE KEJU 65G</t>
+    <t>GURIBEE KEJU 62G</t>
   </si>
   <si>
     <t>20141505</t>
@@ -1516,7 +1510,7 @@
     <t>20047037</t>
   </si>
   <si>
-    <t>IDM KACANG BALI 150G</t>
+    <t>IDM KCANG BALI 150 G</t>
   </si>
   <si>
     <t>20056977</t>
@@ -1966,7 +1960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F237"/>
+  <dimension ref="A1:F236"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2087,21 +2081,21 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -2110,18 +2104,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -2130,18 +2124,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -2150,7 +2144,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
@@ -2158,10 +2152,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -2170,7 +2164,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -2178,10 +2172,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -2190,10 +2184,10 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2207,21 +2201,21 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -2230,7 +2224,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>9</v>
@@ -2238,10 +2232,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -2250,7 +2244,7 @@
         <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>9</v>
@@ -2258,10 +2252,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -2270,10 +2264,10 @@
         <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2290,18 +2284,18 @@
         <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -2310,38 +2304,38 @@
         <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -2350,7 +2344,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>9</v>
@@ -2358,10 +2352,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -2370,7 +2364,7 @@
         <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>9</v>
@@ -2378,10 +2372,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -2390,7 +2384,7 @@
         <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>9</v>
@@ -2398,10 +2392,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -2410,7 +2404,7 @@
         <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>9</v>
@@ -2418,19 +2412,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>9</v>
@@ -2438,19 +2432,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>9</v>
@@ -2458,19 +2452,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>9</v>
@@ -2478,19 +2472,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>9</v>
@@ -2498,19 +2492,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>9</v>
@@ -2518,19 +2512,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>9</v>
@@ -2538,142 +2532,142 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="F35" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2687,53 +2681,53 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2747,13 +2741,13 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2767,13 +2761,13 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2787,33 +2781,33 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2827,13 +2821,13 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2847,13 +2841,13 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2867,13 +2861,13 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2887,10 +2881,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>9</v>
@@ -2907,10 +2901,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>9</v>
@@ -2918,19 +2912,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>9</v>
@@ -2938,22 +2932,22 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2967,13 +2961,13 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2987,13 +2981,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3007,13 +3001,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3027,13 +3021,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3047,10 +3041,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>9</v>
@@ -3067,10 +3061,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>9</v>
@@ -3087,13 +3081,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3107,13 +3101,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3127,13 +3121,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3147,33 +3141,33 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3187,33 +3181,33 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>142</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3227,33 +3221,33 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>42</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3267,13 +3261,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>147</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3287,13 +3281,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -3307,13 +3301,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3327,13 +3321,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3347,10 +3341,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>9</v>
@@ -3367,10 +3361,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>9</v>
@@ -3387,10 +3381,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>9</v>
@@ -3407,10 +3401,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>9</v>
@@ -3427,33 +3421,33 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3467,13 +3461,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3487,13 +3481,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3507,13 +3501,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3527,33 +3521,33 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3567,13 +3561,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3587,10 +3581,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>9</v>
@@ -3607,13 +3601,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3627,30 +3621,30 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>9</v>
@@ -3667,10 +3661,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>9</v>
@@ -3687,13 +3681,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3707,13 +3701,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3727,13 +3721,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3747,33 +3741,33 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3787,13 +3781,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3807,13 +3801,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>137</v>
+        <v>39</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3827,13 +3821,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3847,33 +3841,33 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3887,13 +3881,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3907,13 +3901,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3927,13 +3921,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3947,13 +3941,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3967,33 +3961,33 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -4007,13 +4001,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -4027,13 +4021,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -4047,13 +4041,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4067,33 +4061,33 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4107,13 +4101,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>137</v>
+        <v>39</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4127,13 +4121,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4147,13 +4141,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4167,13 +4161,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E110" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F110" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4187,30 +4181,30 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>9</v>
@@ -4227,10 +4221,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>9</v>
@@ -4247,13 +4241,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -4267,13 +4261,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4287,30 +4281,30 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>9</v>
@@ -4327,10 +4321,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>9</v>
@@ -4347,10 +4341,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>9</v>
@@ -4367,13 +4361,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4387,33 +4381,33 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4427,13 +4421,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4447,13 +4441,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4467,13 +4461,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4487,13 +4481,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4507,33 +4501,33 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4547,13 +4541,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4567,13 +4561,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4587,33 +4581,33 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4627,13 +4621,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4647,13 +4641,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>142</v>
+        <v>39</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4667,13 +4661,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4687,33 +4681,33 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4727,13 +4721,13 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4747,13 +4741,13 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4767,13 +4761,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4787,33 +4781,33 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4827,13 +4821,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4847,13 +4841,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4867,13 +4861,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4887,33 +4881,33 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="E146" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F146" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4927,13 +4921,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4947,13 +4941,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4967,13 +4961,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4987,13 +4981,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -5007,13 +5001,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5027,33 +5021,33 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5067,13 +5061,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5087,13 +5081,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5107,13 +5101,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5127,13 +5121,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E158" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F158" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5147,13 +5141,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5167,33 +5161,33 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="E161" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5207,13 +5201,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5227,10 +5221,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5247,13 +5241,13 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5267,13 +5261,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5287,30 +5281,30 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="E167" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>9</v>
@@ -5327,10 +5321,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>9</v>
@@ -5347,10 +5341,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>9</v>
@@ -5367,10 +5361,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>9</v>
@@ -5387,13 +5381,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E171" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F171" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5407,33 +5401,33 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5447,13 +5441,13 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5467,13 +5461,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5487,13 +5481,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5507,13 +5501,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E177" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F177" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5527,33 +5521,33 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5567,13 +5561,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5587,13 +5581,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5607,13 +5601,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -5627,13 +5621,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -5647,13 +5641,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5667,13 +5661,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5687,13 +5681,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5707,33 +5701,33 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>416</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -5747,13 +5741,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5767,13 +5761,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5787,10 +5781,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>9</v>
@@ -5807,13 +5801,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5827,13 +5821,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -5847,13 +5841,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -5867,33 +5861,33 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="E196" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5907,13 +5901,13 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5927,13 +5921,13 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5947,13 +5941,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -5967,13 +5961,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5987,13 +5981,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6007,33 +6001,33 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="E203" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6047,13 +6041,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6067,13 +6061,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6087,13 +6081,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6107,33 +6101,33 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6147,13 +6141,13 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -6167,13 +6161,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6187,13 +6181,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6207,13 +6201,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6227,13 +6221,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6247,33 +6241,33 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="E215" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6287,13 +6281,13 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6307,13 +6301,13 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -6327,13 +6321,13 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6347,13 +6341,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6367,33 +6361,33 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>487</v>
-      </c>
       <c r="E221" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6407,13 +6401,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6427,13 +6421,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6447,13 +6441,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6467,13 +6461,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6487,13 +6481,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6507,13 +6501,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6527,13 +6521,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6547,13 +6541,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6567,33 +6561,33 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D231" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>508</v>
-      </c>
       <c r="E231" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -6607,13 +6601,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -6627,13 +6621,13 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -6647,13 +6641,13 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -6667,13 +6661,13 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -6687,33 +6681,13 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A237" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="E237" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F237" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -5407,7 +5407,7 @@
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
